--- a/src/attributions/attributions_saliency_traj_467.xlsx
+++ b/src/attributions/attributions_saliency_traj_467.xlsx
@@ -1568,1140 +1568,1140 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.002480538096278906</v>
+        <v>0.002160052070394158</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02940870635211468</v>
+        <v>0.01414402760565281</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000793936662375927</v>
+        <v>0.004058702383190393</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01033361628651619</v>
+        <v>0.001335817854851484</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002056167460978031</v>
+        <v>0.0007430674741044641</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00619181664660573</v>
+        <v>0.01107317768037319</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00149463617708534</v>
+        <v>0.003783668857067823</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005958710098639131</v>
+        <v>0.002850990975275636</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004035090387333184</v>
+        <v>0.004258386790752411</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00417036097496748</v>
+        <v>0.001759982900694013</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01978296414017677</v>
+        <v>0.01770481467247009</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002581805922091007</v>
+        <v>0.005112149752676487</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01129852142184973</v>
+        <v>0.003055647481232882</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007657385896891356</v>
+        <v>0.003428819356486201</v>
       </c>
       <c r="O3" t="n">
-        <v>0.008422692306339741</v>
+        <v>0.009172338992357254</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001412734505720437</v>
+        <v>0.002341213170439005</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.005434825550764799</v>
+        <v>0.001872282708063722</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001009684783639386</v>
+        <v>0.005549866706132889</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001367019372992218</v>
+        <v>0.0003060703165829182</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004123055376112461</v>
+        <v>0.003393817227333784</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001022731885313988</v>
+        <v>0.000819299544673413</v>
       </c>
       <c r="V3" t="n">
-        <v>0.002961775986477733</v>
+        <v>0.002097578952088952</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002687189960852265</v>
+        <v>0.003595034359022975</v>
       </c>
       <c r="X3" t="n">
-        <v>0.002358235418796539</v>
+        <v>3.505738277453929e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001954495906829834</v>
+        <v>0.001030712155625224</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.002304371912032366</v>
+        <v>0.0001291262015001848</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00196302286349237</v>
+        <v>0.001611805520951748</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008924199501052499</v>
+        <v>0.0003083832270931453</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0031127471011132</v>
+        <v>0.001479161437600851</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.002010244177654386</v>
+        <v>0.0009723244002088904</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.001703090965747833</v>
+        <v>0.0004571418976411223</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.00244993157684803</v>
+        <v>0.005065287929028273</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0005380930961109698</v>
+        <v>0.001985345734283328</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.004042265471071005</v>
+        <v>0.002838321961462498</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.00058739073574543</v>
+        <v>0.005015498027205467</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.556942101567984e-05</v>
+        <v>0.0005841733072884381</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0025353510864079</v>
+        <v>0.0008327941177412868</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0044112135656178</v>
+        <v>0.003327004611492157</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.000824029091745615</v>
+        <v>0.0007334614638239145</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.002267534844577312</v>
+        <v>0.0009327419102191925</v>
       </c>
       <c r="AO3" t="n">
-        <v>7.714476669207215e-05</v>
+        <v>0.001472313888370991</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.002840586937963963</v>
+        <v>5.131970101501793e-05</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.632340278476477e-05</v>
+        <v>5.031062755733728e-06</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0006571263074874878</v>
+        <v>0.001526483567431569</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.992672332562506e-05</v>
+        <v>0.0007067420519888401</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.002229462610557675</v>
+        <v>0.0001973523758351803</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.01823326200246811</v>
+        <v>0.0151961101219058</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0009140230831690133</v>
+        <v>0.00314490613527596</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0007566263666376472</v>
+        <v>0.0008958248654380441</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.00596465403214097</v>
+        <v>4.268009797669947e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.001165393157862127</v>
+        <v>0.004665363114327192</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.00265411171130836</v>
+        <v>0.0008985161548480392</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.639157749712467e-05</v>
+        <v>0.003038057824596763</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0004149074957240373</v>
+        <v>0.001996478298678994</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.001132611883804202</v>
+        <v>0.0002888485323637724</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.006444921717047691</v>
+        <v>0.003226801520213485</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.002790469909086823</v>
+        <v>0.001124451169744134</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.003364784177392721</v>
+        <v>0.002665484324097633</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.007701482623815536</v>
+        <v>0.001564241596497595</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.001945315161719918</v>
+        <v>0.0004619225510396063</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.005147724412381649</v>
+        <v>0.001909518614411354</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.004239439964294434</v>
+        <v>0.00256337272003293</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0001196109515149146</v>
+        <v>0.0009145904332399368</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.003999987617135048</v>
+        <v>0.0007392421248368919</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.001702354173175991</v>
+        <v>0.0009339992539025843</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.001243349979631603</v>
+        <v>0.0004545339324977249</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0009826502064242959</v>
+        <v>0.001423714915290475</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.001649270649068058</v>
+        <v>0.003454425372183323</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.311119068413973e-05</v>
+        <v>0.003259549150243402</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0005931832129135728</v>
+        <v>0.002317720092833042</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0009647035039961338</v>
+        <v>4.559244553092867e-05</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.057840412016958e-05</v>
+        <v>0.002062754705548286</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.002429399406537414</v>
+        <v>0.001788576249964535</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.009780196473002434</v>
+        <v>0.0102381044998765</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.0004498141061048955</v>
+        <v>0.0008899973472580314</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.00221717287786305</v>
+        <v>0.003329043975099921</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.001513456576503813</v>
+        <v>0.0004727853229269385</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.004423157311975956</v>
+        <v>0.001570936059579253</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.001199288060888648</v>
+        <v>0.0001232454087585211</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.001340762246400118</v>
+        <v>0.0006029554642736912</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0008669295930303633</v>
+        <v>0.001963873393833637</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.001699427608400583</v>
+        <v>0.0009770183824002743</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.004691726062446833</v>
+        <v>0.003453601151704788</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.001154542434960604</v>
+        <v>8.775216701906174e-05</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0006254524341784418</v>
+        <v>0.0006394670926965773</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0006270414451137185</v>
+        <v>0.0008086954476311803</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.001423551002517343</v>
+        <v>0.001666710595600307</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.001504273852333426</v>
+        <v>0.00075849040877074</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0005564118619076908</v>
+        <v>0.0004677048709709197</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.0008055831422097981</v>
+        <v>0.0001547710271552205</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.001540819415822625</v>
+        <v>0.002303736750036478</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0008091807831078768</v>
+        <v>0.002477792790159583</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.001521818106994033</v>
+        <v>0.001434092642739415</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.003740661544725299</v>
+        <v>0.00141274300403893</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.00259780278429389</v>
+        <v>8.780648931860924e-05</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.003802745370194316</v>
+        <v>0.005575856193900108</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.003782584331929684</v>
+        <v>0.0004196201916784048</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.00491652125492692</v>
+        <v>0.002688557142391801</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.001855824142694473</v>
+        <v>0.0004106777778360993</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.001371136633679271</v>
+        <v>0.0001228483160957694</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.003979175817221403</v>
+        <v>0.003262794110924006</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.001406545867212117</v>
+        <v>0.0001831380068324506</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.001704361755400896</v>
+        <v>0.0005026949220336974</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.001043870346620679</v>
+        <v>0.0006377244717441499</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.002044718712568283</v>
+        <v>0.002257090760394931</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.001336493063718081</v>
+        <v>6.821236456744373e-05</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.0002153347595594823</v>
+        <v>0.0007171447505243123</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.0003821480204351246</v>
+        <v>0.0002038871316472068</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.002134229289367795</v>
+        <v>0.002320034429430962</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.005136957392096519</v>
+        <v>0.003860714845359325</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0005423063412308693</v>
+        <v>0.003682114649564028</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.004400445148348808</v>
+        <v>0.001735396450385451</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.001281901611946523</v>
+        <v>0.002160220174118876</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.003674124134704471</v>
+        <v>0.007932436652481556</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.00404857425019145</v>
+        <v>0.00023943446285557</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.002523910952731967</v>
+        <v>0.004836678504943848</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0005155130638740957</v>
+        <v>0.002492559142410755</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.00218855426646769</v>
+        <v>0.0005855370545759797</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.0009433229570277035</v>
+        <v>0.002395343966782093</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.002014969009906054</v>
+        <v>0.001741077983751893</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.004110273439437151</v>
+        <v>0.001235002651810646</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0009404666488990188</v>
+        <v>7.669551996514201e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.002728165592998266</v>
+        <v>0.001974375918507576</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.0001078755303751677</v>
+        <v>0.000323927728459239</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.001077978871762753</v>
+        <v>0.003499219426885247</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.001343514304608107</v>
+        <v>0.001272080349735916</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.001384287606924772</v>
+        <v>0.0009960222523659468</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0002487244200892746</v>
+        <v>0.001242027967236936</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.003280693665146828</v>
+        <v>0.001476639416068792</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.00224028411321342</v>
+        <v>0.001219522440806031</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.003409556578844786</v>
+        <v>0.001468997914344072</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.0004814468557015061</v>
+        <v>0.00244377925992012</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.001047965721227229</v>
+        <v>0.001377573818899691</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.002384582534432411</v>
+        <v>0.0001572473847772926</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.001045314245857298</v>
+        <v>0.003010001964867115</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.0002693352871574461</v>
+        <v>0.0002130920329364017</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.002452476415783167</v>
+        <v>0.0003898621944244951</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.0001949014113051817</v>
+        <v>0.001440535881556571</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.00163193023763597</v>
+        <v>0.001534331240691245</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0008054529316723347</v>
+        <v>0.001191521994769573</v>
       </c>
       <c r="EK3" t="n">
-        <v>5.322736978996545e-05</v>
+        <v>7.766109774820507e-05</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.002208344172686338</v>
+        <v>0.0006892816163599491</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.0002269386895932257</v>
+        <v>0.000111574656330049</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.0006677790079265833</v>
+        <v>0.001372268539853394</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.0007274296367540956</v>
+        <v>0.0006624831585213542</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.002096687676385045</v>
+        <v>0.002767107682302594</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.0001826624938985333</v>
+        <v>0.000943192164413631</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.001989682205021381</v>
+        <v>0.002190683968365192</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.00142946292180568</v>
+        <v>0.004251133184880018</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.009588179178535938</v>
+        <v>0.004683651495724916</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.001202861429192126</v>
+        <v>0.001597531023435295</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.00128200720064342</v>
+        <v>0.000161543081048876</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.0003700862580444664</v>
+        <v>0.001014811103232205</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.001296759233810008</v>
+        <v>0.0006466166232712567</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.003979731351137161</v>
+        <v>0.003896257374435663</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.0005463312845677137</v>
+        <v>0.0002331707801204175</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.0008553277002647519</v>
+        <v>0.0007514922181144357</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.0008948454633355141</v>
+        <v>0.0002462810953147709</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.001998527674004436</v>
+        <v>0.001754217664711177</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.001576399197801948</v>
+        <v>0.001256258226931095</v>
       </c>
       <c r="FE3" t="n">
-        <v>9.032549132825807e-05</v>
+        <v>0.0003790028276853263</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.0008829435100778937</v>
+        <v>0.0008585998439230025</v>
       </c>
       <c r="FG3" t="n">
-        <v>5.261051410343498e-05</v>
+        <v>0.000184511358384043</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.003825300605967641</v>
+        <v>0.004303195979446173</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.001531101064756513</v>
+        <v>0.002996805123984814</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.003163897432386875</v>
+        <v>0.001852046465501189</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.00274292379617691</v>
+        <v>0.00277761765755713</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.003743656678125262</v>
+        <v>0.002324802102521062</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.0003831065841950476</v>
+        <v>0.0004736507835332304</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.003160936525091529</v>
+        <v>0.006342177279293537</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.001098672626540065</v>
+        <v>0.003996442537754774</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.001674382481724024</v>
+        <v>3.434589598327875e-05</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.002768431324511766</v>
+        <v>0.001373709179461002</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.0008023913251236081</v>
+        <v>0.001591472420841455</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.0007157946238294244</v>
+        <v>0.007985334843397141</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.001884877914562821</v>
+        <v>0.002102572005242109</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.001786320237442851</v>
+        <v>0.001228745561093092</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.003693580627441406</v>
+        <v>0.00189674086868763</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.002079721307381988</v>
+        <v>0.009900877252221107</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.0003068258229177445</v>
+        <v>0.003082060720771551</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.0009396691457368433</v>
+        <v>0.004449208732694387</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.002759796800091863</v>
+        <v>0.0005797641933895648</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.0005422474932856858</v>
+        <v>0.001663505798205733</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.001160595798864961</v>
+        <v>0.0006200019270181656</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.002217820379883051</v>
+        <v>0.0007111256127245724</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.003028747858479619</v>
+        <v>0.0003998772008344531</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.004213269334286451</v>
+        <v>0.0006475176196545362</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.001064350595697761</v>
+        <v>0.001093070604838431</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.0007106479606591165</v>
+        <v>0.002805184805765748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0009828585898503661</v>
+        <v>0.0001921841176226735</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01241762470453978</v>
+        <v>0.01130732893943787</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0009276208584196866</v>
+        <v>0.003517478937283158</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006636457983404398</v>
+        <v>0.008604295551776886</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002081583952531219</v>
+        <v>0.003150947624817491</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003132754005491734</v>
+        <v>0.003493846859782934</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001030539744533598</v>
+        <v>0.004634684417396784</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009053287794813514</v>
+        <v>0.003583173733204603</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007488061091862619</v>
+        <v>0.00069294503191486</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001860988326370716</v>
+        <v>0.0004568185249809176</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00904530007392168</v>
+        <v>0.01277424395084381</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007597928633913398</v>
+        <v>0.004409919958561659</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006422571372240782</v>
+        <v>0.01245101355016232</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003346675308421254</v>
+        <v>0.004154674243181944</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004352869931608438</v>
+        <v>0.0006252243765629828</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0009101036703214049</v>
+        <v>0.004780566319823265</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005425337003543973</v>
+        <v>0.0004149000160396099</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001016268157400191</v>
+        <v>0.0007359512965194881</v>
       </c>
       <c r="S4" t="n">
-        <v>0.000487598852487281</v>
+        <v>0.000390750210499391</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001614448614418507</v>
+        <v>2.614848199300468e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0003578763862606138</v>
+        <v>0.0003013069508597255</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0009719362133182585</v>
+        <v>0.0002075675001833588</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0006969537353143096</v>
+        <v>0.001137043349444866</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001224072533659637</v>
+        <v>0.001483012922108173</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001427053706720471</v>
+        <v>0.0008142574806697667</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0009088608203455806</v>
+        <v>0.001547271618619561</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0004017054452560842</v>
+        <v>0.003001603297889233</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0008552407962270081</v>
+        <v>0.0007650199113413692</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.001799871097318828</v>
+        <v>0.0001528979046270251</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0004244342562742531</v>
+        <v>0.001757385092787445</v>
       </c>
       <c r="AE4" t="n">
-        <v>8.495092333760113e-05</v>
+        <v>0.001950411242432892</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0008319329936057329</v>
+        <v>0.002276219660416245</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0004208704049233347</v>
+        <v>0.002599261701107025</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0004912481526844203</v>
+        <v>0.000390813744161278</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0003439346037339419</v>
+        <v>0.0007084941607899964</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.000375021860236302</v>
+        <v>0.0004889498231932521</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.001280792523175478</v>
+        <v>0.0004124870465602726</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001149368938058615</v>
+        <v>0.003070893697440624</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0001740130974212661</v>
+        <v>0.001432515564374626</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.0003344780998304486</v>
+        <v>0.00176236976403743</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.001303714816458523</v>
+        <v>0.0006009094067849219</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001381546491757035</v>
+        <v>0.00283165043219924</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0003966385556850582</v>
+        <v>0.001297020120546222</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0009416078682988882</v>
+        <v>0.0006903862813487649</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0007905617821961641</v>
+        <v>0.0001148624578490853</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.001014181296341121</v>
+        <v>0.0005187913193367422</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0095910569652915</v>
+        <v>0.0077251554466784</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0001308348291786388</v>
+        <v>0.0008120153797790408</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001776147400960326</v>
+        <v>0.004623127169907093</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0009303377009928226</v>
+        <v>0.007530594244599342</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.692554158391431e-06</v>
+        <v>0.0007211554329842329</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.000484288641018793</v>
+        <v>0.0004163244157098234</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0005460440297611058</v>
+        <v>0.0007203633431345224</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0005218727746978402</v>
+        <v>0.000945757667068392</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.000306907226331532</v>
+        <v>1.184700522571802e-06</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.00261463038623333</v>
+        <v>0.001523195882327855</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002720680553466082</v>
+        <v>0.002739355433732271</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.001282431301660836</v>
+        <v>0.0009461474255658686</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.003103091847151518</v>
+        <v>0.0006304280832409859</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.002779057249426842</v>
+        <v>0.001668138429522514</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001770226284861565</v>
+        <v>0.001212243107147515</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0002820865483954549</v>
+        <v>0.003181552514433861</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0007635449292138219</v>
+        <v>0.001751320669427514</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001210669288411736</v>
+        <v>0.0004191931511741132</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.002195078413933516</v>
+        <v>0.000337067642249167</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.001000964315608144</v>
+        <v>0.001356454798951745</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0001884739613160491</v>
+        <v>0.001739584491588175</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.001693446072749794</v>
+        <v>0.0009397425455972552</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.001036362489685416</v>
+        <v>0.0003435977560002357</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0002013640769291669</v>
+        <v>6.136148294899613e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0001761673483997583</v>
+        <v>0.001130758784711361</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0004661669954657555</v>
+        <v>0.000456704874522984</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.00096558325458318</v>
+        <v>0.0002576828701421618</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.004606315400451422</v>
+        <v>0.005153527017682791</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.001287089427933097</v>
+        <v>0.001070787315256894</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001157933962531388</v>
+        <v>0.004060254897922277</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.278708416270092e-05</v>
+        <v>0.002455238718539476</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002248747274279594</v>
+        <v>0.001603982294909656</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.817368118092418e-05</v>
+        <v>0.001629559556022286</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0008818897185847163</v>
+        <v>7.229682523757219e-05</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.000567696348298341</v>
+        <v>0.001973687205463648</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0004828374949283898</v>
+        <v>0.0001575467322254553</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001998509280383587</v>
+        <v>0.003598429495468736</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0008293811115436256</v>
+        <v>0.001191559480503201</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0006290770252235234</v>
+        <v>0.003184809815138578</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0002895311627071351</v>
+        <v>0.0003125214716419578</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0007754099788144231</v>
+        <v>0.000592063064686954</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0005465337308123708</v>
+        <v>0.0002042886335402727</v>
       </c>
       <c r="CK4" t="n">
-        <v>5.384950782172382e-05</v>
+        <v>0.0002599171421024948</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.0001081629598047584</v>
+        <v>0.0006491719977930188</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001926814205944538</v>
+        <v>3.250571899116039e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.001508647110313177</v>
+        <v>0.003236988559365273</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0002486759913153946</v>
+        <v>0.002628996968269348</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.001627822057344019</v>
+        <v>0.004086457658559084</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.001676248968578875</v>
+        <v>0.001942951930686831</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.001118429587222636</v>
+        <v>0.0008297098102048039</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.001210314687341452</v>
+        <v>0.0007868149550631642</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.002728533232584596</v>
+        <v>0.001030378043651581</v>
       </c>
       <c r="CU4" t="n">
-        <v>3.847131301881745e-05</v>
+        <v>0.001735668396577239</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0003554206632543355</v>
+        <v>7.237118552438915e-05</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.001482958206906915</v>
+        <v>0.003575995564460754</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.001122927293181419</v>
+        <v>0.001230840221978724</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.00114675925578922</v>
+        <v>0.003467253409326077</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0001904869277495891</v>
+        <v>0.00083213608013466</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0007399629685096443</v>
+        <v>0.000563338806387037</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0004317501443438232</v>
+        <v>0.0004397507873363793</v>
       </c>
       <c r="DC4" t="n">
-        <v>4.460429772734642e-05</v>
+        <v>1.619703834876418e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.349778125993907e-06</v>
+        <v>0.001081970287486911</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001050392049364746</v>
+        <v>0.001623676274903119</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.00178008689545095</v>
+        <v>0.001973211765289307</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001327770412899554</v>
+        <v>0.0006828954210504889</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.003462971188127995</v>
+        <v>0.002826885785907507</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0005187794449739158</v>
+        <v>0.0001172299089375883</v>
       </c>
       <c r="DJ4" t="n">
-        <v>7.406866643577814e-05</v>
+        <v>0.005151986610144377</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0008698457386344671</v>
+        <v>0.001742677646689117</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0004302870365791023</v>
+        <v>0.004760858602821827</v>
       </c>
       <c r="DM4" t="n">
-        <v>7.435475708916783e-05</v>
+        <v>0.001821975689381361</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.0009394827065989375</v>
+        <v>0.0002175841946154833</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0003285812272224575</v>
+        <v>0.001324748620390892</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0009298459044657648</v>
+        <v>0.001512684859335423</v>
       </c>
       <c r="DQ4" t="n">
-        <v>7.096467743394896e-05</v>
+        <v>0.001427837181836367</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.000493092811666429</v>
+        <v>0.0008763766963966191</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0007191691547632217</v>
+        <v>0.001593078719452024</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0001906403922475874</v>
+        <v>0.00153977214358747</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0003740742686204612</v>
+        <v>0.001425664289854467</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0003597299801185727</v>
+        <v>0.004879952408373356</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0002026832662522793</v>
+        <v>0.0002273875870741904</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0003586802049539983</v>
+        <v>0.0006374500808306038</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.001649601268582046</v>
+        <v>0.0001432708959328011</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0002303936926182359</v>
+        <v>0.0008359665516763926</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.001484930398873985</v>
+        <v>0.001367927878163755</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0008434390183538198</v>
+        <v>0.002620755229145288</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0005546167958527803</v>
+        <v>0.0001112270401790738</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0005608557257801294</v>
+        <v>0.005540418904274702</v>
       </c>
       <c r="EE4" t="n">
-        <v>7.56137742428109e-05</v>
+        <v>0.004101454745978117</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0002563996240496635</v>
+        <v>0.0008349685231223702</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.00145171582698822</v>
+        <v>0.002587595256045461</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0002773050800897181</v>
+        <v>0.0005657359724864364</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001348095946013927</v>
+        <v>0.003255671123042703</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0004601414548233151</v>
+        <v>0.0003855951654259115</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0006117760203778744</v>
+        <v>0.0003193621523678303</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0004491424188017845</v>
+        <v>1.519567740615457e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0002780033100862056</v>
+        <v>0.0003449911600910127</v>
       </c>
       <c r="EN4" t="n">
-        <v>5.829521978739649e-05</v>
+        <v>0.0004939726204611361</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0006186222890391946</v>
+        <v>0.0006793062784709036</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.001284504309296608</v>
+        <v>0.0028051040135324</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0007130192243494093</v>
+        <v>0.0006429962813854218</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.001021295669488609</v>
+        <v>0.001629245583899319</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0002097804099321365</v>
+        <v>0.0005616603302769363</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.003146878443658352</v>
+        <v>0.0006201451178640127</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001053668325766921</v>
+        <v>0.001112406724132597</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0009570301044732332</v>
+        <v>0.0003783762804232538</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0005014801281504333</v>
+        <v>0.002601960208266973</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0001539643853902817</v>
+        <v>0.0001802915940061212</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.001574311754666269</v>
+        <v>0.003904703073203564</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0005775340832769871</v>
+        <v>0.0009991694241762161</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0009060450829565525</v>
+        <v>0.003480108920484781</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.0001151155302068219</v>
+        <v>0.0005149095086380839</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.001012123306281865</v>
+        <v>0.0008812841260805726</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.0005998242413625121</v>
+        <v>0.0005215941346250474</v>
       </c>
       <c r="FE4" t="n">
-        <v>7.690800703130662e-05</v>
+        <v>0.0003562652855180204</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0001496947952546179</v>
+        <v>0.001093531958758831</v>
       </c>
       <c r="FG4" t="n">
-        <v>9.27780638448894e-05</v>
+        <v>0.0001540714874863625</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0001619995600776747</v>
+        <v>0.001906574470922351</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.0005087535828351974</v>
+        <v>0.001611727057024837</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.001183898188173771</v>
+        <v>0.002453964669257402</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0006712343893013895</v>
+        <v>0.0004828273667953908</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0001217303215526044</v>
+        <v>0.001299000228755176</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0006331696640700102</v>
+        <v>0.0008852160535752773</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0003613881708588451</v>
+        <v>0.001399425673298538</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0004681324353441596</v>
+        <v>0.001670020283199847</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.0007214811630547047</v>
+        <v>0.002014525467529893</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.001397894462570548</v>
+        <v>0.004075614269822836</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.000275239406619221</v>
+        <v>0.001052495557814837</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.00117780186701566</v>
+        <v>0.003046216908842325</v>
       </c>
       <c r="FT4" t="n">
-        <v>8.477340452373028e-05</v>
+        <v>0.0010014190338552</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0003726488212123513</v>
+        <v>0.002525073476135731</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.0007157358340919018</v>
+        <v>5.107925971969962e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0002402584505034611</v>
+        <v>0.002559161279350519</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0008710699039511383</v>
+        <v>0.003549929009750485</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.00136818434111774</v>
+        <v>0.001242417492903769</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0005784143577329814</v>
+        <v>0.002041572704911232</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.0003310754254925996</v>
+        <v>0.0002160035073757172</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0005721320630982518</v>
+        <v>0.002328726928681135</v>
       </c>
       <c r="GC4" t="n">
-        <v>8.779834024608135e-05</v>
+        <v>0.003665786935016513</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.001127603929489851</v>
+        <v>0.0004495297325775027</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.002714056055992842</v>
+        <v>0.002715383190661669</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0006193508743308485</v>
+        <v>0.00118208141066134</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0002857213257811964</v>
+        <v>0.0009264391846954823</v>
       </c>
     </row>
     <row r="5">
@@ -3275,1709 +3275,1709 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2.270957644157079e-09</v>
+        <v>1.560007956147302e-10</v>
       </c>
       <c r="B6" t="n">
-        <v>1.69722511600412e-08</v>
+        <v>8.14313949604184e-10</v>
       </c>
       <c r="C6" t="n">
-        <v>7.243979305293635e-10</v>
+        <v>1.546944100594416e-10</v>
       </c>
       <c r="D6" t="n">
-        <v>3.097690282061194e-08</v>
+        <v>8.615341773321461e-11</v>
       </c>
       <c r="E6" t="n">
-        <v>2.081056660330205e-09</v>
+        <v>5.751651932506263e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>7.42652606078309e-10</v>
+        <v>1.554997797192925e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>2.016395383996894e-10</v>
+        <v>1.562430462787034e-10</v>
       </c>
       <c r="H6" t="n">
-        <v>5.610006348355512e-10</v>
+        <v>6.192332757670727e-11</v>
       </c>
       <c r="I6" t="n">
-        <v>3.429724504400156e-09</v>
+        <v>7.630486520415758e-11</v>
       </c>
       <c r="J6" t="n">
-        <v>5.643890688133979e-09</v>
+        <v>4.732904346216316e-11</v>
       </c>
       <c r="K6" t="n">
-        <v>1.056985077241279e-08</v>
+        <v>1.20513998780325e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>7.940698654174128e-10</v>
+        <v>2.638715912439693e-10</v>
       </c>
       <c r="M6" t="n">
-        <v>1.556842299521577e-08</v>
+        <v>2.144106003854063e-10</v>
       </c>
       <c r="N6" t="n">
-        <v>4.989872515182014e-09</v>
+        <v>8.092767567191572e-10</v>
       </c>
       <c r="O6" t="n">
-        <v>6.518327655413714e-09</v>
+        <v>9.073375731305511e-12</v>
       </c>
       <c r="P6" t="n">
-        <v>5.986768858434743e-09</v>
+        <v>1.023527096410959e-11</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.409034192245144e-09</v>
+        <v>4.045536683427997e-10</v>
       </c>
       <c r="R6" t="n">
-        <v>5.144975556703457e-10</v>
+        <v>2.055413755863711e-10</v>
       </c>
       <c r="S6" t="n">
-        <v>1.268471994109177e-09</v>
+        <v>1.373822496736343e-12</v>
       </c>
       <c r="T6" t="n">
-        <v>3.713150453776848e-09</v>
+        <v>1.140321170822745e-10</v>
       </c>
       <c r="U6" t="n">
-        <v>9.930656297285623e-11</v>
+        <v>5.324177557164411e-11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.126336246493054e-09</v>
+        <v>1.573486618777764e-10</v>
       </c>
       <c r="W6" t="n">
-        <v>6.58696475142051e-09</v>
+        <v>1.38516809133904e-10</v>
       </c>
       <c r="X6" t="n">
-        <v>3.871509779429516e-09</v>
+        <v>2.152659647758348e-11</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.051758236059186e-08</v>
+        <v>1.269646610069231e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.033767376730111e-09</v>
+        <v>4.593894709081781e-14</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.664363035227325e-09</v>
+        <v>2.214333716388239e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.098581391469679e-10</v>
+        <v>1.528168980247102e-10</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.079562217398689e-09</v>
+        <v>1.643183367150414e-10</v>
       </c>
       <c r="AD6" t="n">
-        <v>6.03763983253458e-11</v>
+        <v>3.694154010469575e-11</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.432575779171998e-09</v>
+        <v>1.291349804866115e-10</v>
       </c>
       <c r="AF6" t="n">
-        <v>6.156677834212587e-09</v>
+        <v>4.106500139933189e-10</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.421532917575632e-09</v>
+        <v>2.680028698964776e-10</v>
       </c>
       <c r="AH6" t="n">
-        <v>5.72587088853993e-10</v>
+        <v>3.684832300399066e-11</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.106633978371519e-09</v>
+        <v>3.226455491667224e-10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.946380168149631e-09</v>
+        <v>5.39680106159679e-11</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.855187448107642e-09</v>
+        <v>4.745051573884496e-12</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.33000271801609e-09</v>
+        <v>1.23021037801152e-10</v>
       </c>
       <c r="AM6" t="n">
-        <v>8.81370587624275e-10</v>
+        <v>1.154631321109711e-10</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.629376494311941e-09</v>
+        <v>1.914196232077892e-11</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.456910259101107e-09</v>
+        <v>1.063248794563876e-10</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.751204514732763e-09</v>
+        <v>1.377941649671754e-10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.997823849744009e-09</v>
+        <v>9.150015467529471e-11</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.876784283538768e-09</v>
+        <v>1.529805102040704e-11</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.849969399891904e-09</v>
+        <v>6.241802213979852e-11</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.042581824847957e-10</v>
+        <v>9.155391722526218e-12</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.184863370923722e-09</v>
+        <v>1.006839500661272e-09</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.735274477558505e-10</v>
+        <v>9.988614102507398e-11</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.942869687354687e-08</v>
+        <v>1.246509839791798e-10</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.350718173564474e-09</v>
+        <v>3.572334095203189e-10</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.886624272946392e-09</v>
+        <v>7.039292065913472e-11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.99341332119252e-09</v>
+        <v>1.745083244575341e-11</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.328328001041882e-09</v>
+        <v>1.352837425416809e-10</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.647308760041824e-09</v>
+        <v>1.282071671049323e-10</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.379409697577216e-09</v>
+        <v>1.068911278934159e-11</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.01443128844403e-09</v>
+        <v>2.517786812372691e-10</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.480917027369856e-09</v>
+        <v>2.519329189709651e-10</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.42002418104903e-10</v>
+        <v>1.067021332401552e-10</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.753341554750932e-09</v>
+        <v>8.749559410325958e-11</v>
       </c>
       <c r="BH6" t="n">
-        <v>2.452535730057548e-09</v>
+        <v>3.46622452962464e-11</v>
       </c>
       <c r="BI6" t="n">
-        <v>4.542012543851115e-09</v>
+        <v>6.746203595753286e-11</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.791367716616151e-09</v>
+        <v>2.905506946149217e-10</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.41687048152528e-09</v>
+        <v>1.416654155095287e-10</v>
       </c>
       <c r="BL6" t="n">
-        <v>3.503221046585736e-10</v>
+        <v>7.757917919182233e-11</v>
       </c>
       <c r="BM6" t="n">
-        <v>2.11313952447334e-11</v>
+        <v>3.697997186247193e-10</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.439532380080436e-09</v>
+        <v>6.586600709290735e-11</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.141293393125409e-09</v>
+        <v>1.089653714481109e-11</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.12903142180221e-09</v>
+        <v>3.883749988276008e-10</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.838930424076125e-09</v>
+        <v>1.209569389093446e-10</v>
       </c>
       <c r="BR6" t="n">
-        <v>1.904896462789907e-09</v>
+        <v>2.421607636637901e-10</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.926149100801467e-09</v>
+        <v>1.463264648338125e-10</v>
       </c>
       <c r="BT6" t="n">
-        <v>1.454536935341366e-09</v>
+        <v>5.264272004423809e-11</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.451153500286466e-10</v>
+        <v>8.833305614741604e-11</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.652582402149164e-09</v>
+        <v>6.554040643536041e-10</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.000347443242845e-09</v>
+        <v>1.677383232312479e-11</v>
       </c>
       <c r="BX6" t="n">
-        <v>7.803050650068144e-09</v>
+        <v>1.128792753712915e-10</v>
       </c>
       <c r="BY6" t="n">
-        <v>4.491797600536529e-09</v>
+        <v>1.604203714311581e-10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1.847351716044443e-10</v>
+        <v>8.820144614674064e-11</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.496104072908679e-09</v>
+        <v>2.588665393155054e-10</v>
       </c>
       <c r="CB6" t="n">
-        <v>2.012280342356121e-09</v>
+        <v>1.443723335325942e-10</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.317205704040816e-09</v>
+        <v>1.936236726507445e-10</v>
       </c>
       <c r="CD6" t="n">
-        <v>5.555398363554787e-10</v>
+        <v>5.15630801944944e-11</v>
       </c>
       <c r="CE6" t="n">
-        <v>2.56876742099621e-09</v>
+        <v>3.015280247709029e-10</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.927950992770434e-09</v>
+        <v>3.75314952727468e-11</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.437959250618405e-09</v>
+        <v>7.74129892133768e-12</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.32867628011013e-09</v>
+        <v>2.020858203000131e-10</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.009641745208789e-10</v>
+        <v>6.167811400503709e-11</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.30050903379697e-09</v>
+        <v>1.594561808981876e-11</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.126950865959486e-09</v>
+        <v>7.331733831161813e-11</v>
       </c>
       <c r="CL6" t="n">
-        <v>3.081433552765134e-09</v>
+        <v>7.275428870467948e-11</v>
       </c>
       <c r="CM6" t="n">
-        <v>3.611400511971397e-09</v>
+        <v>2.829078915578265e-10</v>
       </c>
       <c r="CN6" t="n">
-        <v>4.294759214928945e-09</v>
+        <v>6.138605179728529e-10</v>
       </c>
       <c r="CO6" t="n">
-        <v>4.444315471197058e-10</v>
+        <v>1.821032213911167e-10</v>
       </c>
       <c r="CP6" t="n">
-        <v>3.82372267182518e-09</v>
+        <v>1.678489985890153e-10</v>
       </c>
       <c r="CQ6" t="n">
-        <v>1.02777641952656e-09</v>
+        <v>7.99441068899398e-12</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.811156558062521e-09</v>
+        <v>2.451575886741608e-10</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.984619745267537e-09</v>
+        <v>1.429561469201701e-10</v>
       </c>
       <c r="CT6" t="n">
-        <v>1.398451399126088e-08</v>
+        <v>1.355976789185753e-11</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.574323560404878e-09</v>
+        <v>1.097606033839682e-10</v>
       </c>
       <c r="CV6" t="n">
-        <v>4.428178101978375e-10</v>
+        <v>2.920774733183862e-12</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.344104910179112e-09</v>
+        <v>2.937159959692792e-10</v>
       </c>
       <c r="CX6" t="n">
-        <v>2.282960931410116e-09</v>
+        <v>5.86528742241299e-11</v>
       </c>
       <c r="CY6" t="n">
-        <v>5.995360652377713e-09</v>
+        <v>6.394222651362469e-11</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.067513493742013e-09</v>
+        <v>1.736226995507906e-10</v>
       </c>
       <c r="DA6" t="n">
-        <v>4.80149087156434e-10</v>
+        <v>5.802149039002558e-11</v>
       </c>
       <c r="DB6" t="n">
-        <v>5.381162182516164e-10</v>
+        <v>3.319634497844781e-11</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.078948930199886e-09</v>
+        <v>9.410403012388713e-11</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.132343190908159e-09</v>
+        <v>1.165487428789191e-10</v>
       </c>
       <c r="DE6" t="n">
-        <v>3.204592369243642e-09</v>
+        <v>1.446257558157527e-10</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.929538473444126e-10</v>
+        <v>1.294686718944504e-10</v>
       </c>
       <c r="DG6" t="n">
-        <v>6.905413130198212e-09</v>
+        <v>5.463968166807831e-11</v>
       </c>
       <c r="DH6" t="n">
-        <v>1.956949802206509e-08</v>
+        <v>6.879114639035677e-11</v>
       </c>
       <c r="DI6" t="n">
-        <v>8.926531513964164e-09</v>
+        <v>3.469259948762904e-11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.270641369899295e-10</v>
+        <v>1.647178782260283e-10</v>
       </c>
       <c r="DK6" t="n">
-        <v>6.366768889876084e-09</v>
+        <v>7.369530680145786e-11</v>
       </c>
       <c r="DL6" t="n">
-        <v>1.449329189995296e-08</v>
+        <v>2.416613298361625e-10</v>
       </c>
       <c r="DM6" t="n">
-        <v>3.808410253824945e-10</v>
+        <v>8.840450593794458e-11</v>
       </c>
       <c r="DN6" t="n">
-        <v>4.941517750545188e-10</v>
+        <v>6.585278156112651e-11</v>
       </c>
       <c r="DO6" t="n">
-        <v>6.106687933105093e-10</v>
+        <v>1.576414138115823e-10</v>
       </c>
       <c r="DP6" t="n">
-        <v>4.423536204001266e-09</v>
+        <v>7.403921920001721e-11</v>
       </c>
       <c r="DQ6" t="n">
-        <v>3.71230113316301e-09</v>
+        <v>9.963974090254624e-11</v>
       </c>
       <c r="DR6" t="n">
-        <v>2.976133561816141e-09</v>
+        <v>7.083312235367512e-12</v>
       </c>
       <c r="DS6" t="n">
-        <v>3.050377950231109e-09</v>
+        <v>1.962175144587519e-10</v>
       </c>
       <c r="DT6" t="n">
-        <v>9.455171090522185e-10</v>
+        <v>6.115412343188353e-11</v>
       </c>
       <c r="DU6" t="n">
-        <v>7.132394119757635e-10</v>
+        <v>3.499348033564331e-11</v>
       </c>
       <c r="DV6" t="n">
-        <v>5.151413517978654e-09</v>
+        <v>8.346769803102561e-11</v>
       </c>
       <c r="DW6" t="n">
-        <v>6.736547986108121e-10</v>
+        <v>7.415082436956766e-11</v>
       </c>
       <c r="DX6" t="n">
-        <v>5.837549110765394e-09</v>
+        <v>3.237061174665712e-10</v>
       </c>
       <c r="DY6" t="n">
-        <v>2.769275697644957e-09</v>
+        <v>2.00095062047323e-11</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.140520649618338e-09</v>
+        <v>1.297459362170628e-10</v>
       </c>
       <c r="EA6" t="n">
-        <v>7.555020609117946e-09</v>
+        <v>5.206897135678901e-10</v>
       </c>
       <c r="EB6" t="n">
-        <v>4.249982588078183e-09</v>
+        <v>8.58726284524991e-12</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.177591357759411e-09</v>
+        <v>6.414777042884623e-11</v>
       </c>
       <c r="ED6" t="n">
-        <v>2.704305224199288e-09</v>
+        <v>2.434523693750634e-10</v>
       </c>
       <c r="EE6" t="n">
-        <v>1.788403314328946e-09</v>
+        <v>2.879857741167058e-10</v>
       </c>
       <c r="EF6" t="n">
-        <v>1.334017896148509e-09</v>
+        <v>8.67973540263911e-11</v>
       </c>
       <c r="EG6" t="n">
-        <v>2.412897659453961e-10</v>
+        <v>5.704432065600784e-11</v>
       </c>
       <c r="EH6" t="n">
-        <v>1.527795778777374e-09</v>
+        <v>4.418027402253166e-11</v>
       </c>
       <c r="EI6" t="n">
-        <v>4.955610588552872e-09</v>
+        <v>8.219740166293121e-11</v>
       </c>
       <c r="EJ6" t="n">
-        <v>2.998583381597086e-09</v>
+        <v>5.803291874828531e-11</v>
       </c>
       <c r="EK6" t="n">
-        <v>5.684587800480756e-10</v>
+        <v>8.494214359666685e-11</v>
       </c>
       <c r="EL6" t="n">
-        <v>8.399044792994914e-10</v>
+        <v>7.068953061795114e-11</v>
       </c>
       <c r="EM6" t="n">
-        <v>1.5653571772134e-09</v>
+        <v>7.942254492965262e-11</v>
       </c>
       <c r="EN6" t="n">
-        <v>1.493554280251885e-09</v>
+        <v>1.771611884970881e-10</v>
       </c>
       <c r="EO6" t="n">
-        <v>9.6629004797677e-10</v>
+        <v>7.49459730386981e-11</v>
       </c>
       <c r="EP6" t="n">
-        <v>9.762283204040045e-10</v>
+        <v>1.316309145016348e-10</v>
       </c>
       <c r="EQ6" t="n">
-        <v>2.588678826853652e-09</v>
+        <v>1.71020350658857e-11</v>
       </c>
       <c r="ER6" t="n">
-        <v>2.843739466129591e-09</v>
+        <v>2.419203726233832e-12</v>
       </c>
       <c r="ES6" t="n">
-        <v>1.143183148144544e-08</v>
+        <v>4.792123989294517e-11</v>
       </c>
       <c r="ET6" t="n">
-        <v>1.716329300904818e-10</v>
+        <v>7.00849517309976e-11</v>
       </c>
       <c r="EU6" t="n">
-        <v>6.657298601275841e-10</v>
+        <v>1.280432530836872e-11</v>
       </c>
       <c r="EV6" t="n">
-        <v>4.362514349764979e-09</v>
+        <v>1.239769120697787e-10</v>
       </c>
       <c r="EW6" t="n">
-        <v>3.519905478199803e-10</v>
+        <v>1.416169959078672e-10</v>
       </c>
       <c r="EX6" t="n">
-        <v>1.220063161611051e-09</v>
+        <v>3.387311958702455e-11</v>
       </c>
       <c r="EY6" t="n">
-        <v>2.663467224550686e-09</v>
+        <v>3.245414492702992e-10</v>
       </c>
       <c r="EZ6" t="n">
-        <v>2.618745220672736e-09</v>
+        <v>3.045652618993699e-11</v>
       </c>
       <c r="FA6" t="n">
-        <v>5.005321934703488e-09</v>
+        <v>3.88409721052696e-11</v>
       </c>
       <c r="FB6" t="n">
-        <v>1.16935972016563e-09</v>
+        <v>1.327651460991675e-10</v>
       </c>
       <c r="FC6" t="n">
-        <v>7.478542229932827e-10</v>
+        <v>7.804436263914027e-11</v>
       </c>
       <c r="FD6" t="n">
-        <v>1.21424847954188e-09</v>
+        <v>2.915633012801067e-11</v>
       </c>
       <c r="FE6" t="n">
-        <v>1.191473919526231e-09</v>
+        <v>1.003518379505408e-10</v>
       </c>
       <c r="FF6" t="n">
-        <v>3.168578288637036e-09</v>
+        <v>1.40052650032807e-10</v>
       </c>
       <c r="FG6" t="n">
-        <v>1.145798567137035e-09</v>
+        <v>8.153462627280561e-11</v>
       </c>
       <c r="FH6" t="n">
-        <v>1.343182898239093e-09</v>
+        <v>3.945339888122845e-11</v>
       </c>
       <c r="FI6" t="n">
-        <v>4.429608679856756e-09</v>
+        <v>1.340838273744538e-10</v>
       </c>
       <c r="FJ6" t="n">
-        <v>8.1506623672567e-09</v>
+        <v>2.450941671838791e-10</v>
       </c>
       <c r="FK6" t="n">
-        <v>2.711676660993589e-09</v>
+        <v>6.660695606175437e-11</v>
       </c>
       <c r="FL6" t="n">
-        <v>1.523731585351129e-09</v>
+        <v>1.352785244934651e-10</v>
       </c>
       <c r="FM6" t="n">
-        <v>6.745779934647089e-09</v>
+        <v>6.180211897799381e-11</v>
       </c>
       <c r="FN6" t="n">
-        <v>2.078452299159039e-09</v>
+        <v>1.202333510530451e-10</v>
       </c>
       <c r="FO6" t="n">
-        <v>2.788446584744975e-09</v>
+        <v>1.7553833386863e-10</v>
       </c>
       <c r="FP6" t="n">
-        <v>3.582608210095373e-09</v>
+        <v>1.530957305373448e-10</v>
       </c>
       <c r="FQ6" t="n">
-        <v>2.259338049981352e-09</v>
+        <v>1.80180814712827e-10</v>
       </c>
       <c r="FR6" t="n">
-        <v>5.996675378483474e-10</v>
+        <v>1.96138799646306e-11</v>
       </c>
       <c r="FS6" t="n">
-        <v>5.77611847241144e-10</v>
+        <v>1.873769334137521e-10</v>
       </c>
       <c r="FT6" t="n">
-        <v>7.337473295621066e-09</v>
+        <v>2.550775424214891e-10</v>
       </c>
       <c r="FU6" t="n">
-        <v>2.902427187478906e-09</v>
+        <v>1.305575092480638e-10</v>
       </c>
       <c r="FV6" t="n">
-        <v>3.768966028161458e-09</v>
+        <v>1.20085330568287e-10</v>
       </c>
       <c r="FW6" t="n">
-        <v>6.790213946672452e-10</v>
+        <v>1.776862823543723e-10</v>
       </c>
       <c r="FX6" t="n">
-        <v>2.417665623255516e-09</v>
+        <v>8.179279475939438e-11</v>
       </c>
       <c r="FY6" t="n">
-        <v>4.906852701935804e-09</v>
+        <v>7.455965705949197e-11</v>
       </c>
       <c r="FZ6" t="n">
-        <v>2.103322627178272e-09</v>
+        <v>1.206198335657049e-10</v>
       </c>
       <c r="GA6" t="n">
-        <v>2.019933331709467e-09</v>
+        <v>8.586398259069483e-11</v>
       </c>
       <c r="GB6" t="n">
-        <v>1.376347036341485e-09</v>
+        <v>3.043161903026892e-11</v>
       </c>
       <c r="GC6" t="n">
-        <v>6.186919865314167e-10</v>
+        <v>2.787836350659489e-10</v>
       </c>
       <c r="GD6" t="n">
-        <v>1.461768928123774e-09</v>
+        <v>1.642413427482836e-10</v>
       </c>
       <c r="GE6" t="n">
-        <v>8.08846589706036e-09</v>
+        <v>2.677626176339487e-10</v>
       </c>
       <c r="GF6" t="n">
-        <v>1.118642511954704e-09</v>
+        <v>5.164719346639757e-12</v>
       </c>
       <c r="GG6" t="n">
-        <v>2.423667933015849e-09</v>
+        <v>1.614002820282678e-10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0005916834343224764</v>
+        <v>8.886676369002089e-06</v>
       </c>
       <c r="B7" t="n">
-        <v>0.004438782576471567</v>
+        <v>2.120139106409624e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>4.768528378917836e-05</v>
+        <v>5.150316610524897e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00252829841338098</v>
+        <v>4.468347924557747e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009419451234862208</v>
+        <v>1.600941322976723e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002597602782770991</v>
+        <v>4.213869942759629e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002836819330696017</v>
+        <v>1.988601525226841e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0005536895478144288</v>
+        <v>1.329532460658811e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.077023135730997e-05</v>
+        <v>8.048228892221232e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001145927468314767</v>
+        <v>5.865626008016989e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003035661764442921</v>
+        <v>3.654442116385326e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0005016418872401118</v>
+        <v>4.383308805699926e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002707098377868533</v>
+        <v>1.573236295371316e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001616312307305634</v>
+        <v>2.301900531165302e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003468028269708157</v>
+        <v>3.100142293988029e-06</v>
       </c>
       <c r="P7" t="n">
-        <v>5.357745249057189e-05</v>
+        <v>7.486201866413467e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.377536919899285e-05</v>
+        <v>8.459403488814132e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0001236910466104746</v>
+        <v>5.004764716431964e-06</v>
       </c>
       <c r="S7" t="n">
-        <v>0.000444078556029126</v>
+        <v>1.17359832074726e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0007147785509005189</v>
+        <v>8.048232302826364e-07</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001222066057380289</v>
+        <v>1.167191612694296e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0005501176347024739</v>
+        <v>4.575382718030596e-06</v>
       </c>
       <c r="W7" t="n">
-        <v>7.009821274550632e-05</v>
+        <v>6.811838829889894e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0003892426611855626</v>
+        <v>2.023491560976254e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0003755130455829203</v>
+        <v>1.005434569378849e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.036923827603459e-05</v>
+        <v>7.957582965900656e-06</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002914825745392591</v>
+        <v>1.575337819303968e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0002322934160474688</v>
+        <v>5.297012648952659e-06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0008784595993347466</v>
+        <v>2.623939053592039e-06</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0001572260953253135</v>
+        <v>8.273095204458514e-07</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0002343910455238074</v>
+        <v>1.876921714938362e-06</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.001041162759065628</v>
+        <v>7.826842193026096e-06</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0006082002655602992</v>
+        <v>7.417492042804952e-07</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0004435412120074034</v>
+        <v>6.765573743905406e-06</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0006703108083456755</v>
+        <v>1.754914774210192e-05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5.95259916735813e-05</v>
+        <v>3.165478119626641e-06</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.000358782010152936</v>
+        <v>1.643554924157797e-06</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0006576689193025231</v>
+        <v>2.231027110610739e-06</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.909964966122061e-05</v>
+        <v>2.878565510400222e-06</v>
       </c>
       <c r="AN7" t="n">
-        <v>5.278065509628505e-05</v>
+        <v>5.747798468291876e-07</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.524917024653405e-05</v>
+        <v>5.371486622607335e-06</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0006242575473152101</v>
+        <v>2.870829121093266e-06</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.000235490093473345</v>
+        <v>1.054435756486782e-07</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0002472518244758248</v>
+        <v>6.588877567992313e-06</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0005146473413333297</v>
+        <v>6.534177714456746e-07</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0005399301880970597</v>
+        <v>3.999330601800466e-06</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.003254615468904376</v>
+        <v>2.88786250166595e-05</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.000232301201322116</v>
+        <v>4.239424924890045e-06</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.649660645052791e-05</v>
+        <v>1.704674559732666e-06</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0004725870385300368</v>
+        <v>1.561310273245908e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001212977222166955</v>
+        <v>9.100083843804896e-06</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0002487486344762146</v>
+        <v>5.173287718207575e-07</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0006159049225971103</v>
+        <v>1.358455619993038e-06</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0003905503253918141</v>
+        <v>7.207130465758382e-07</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0004446863604243845</v>
+        <v>9.173370472126408e-07</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0006468833307735622</v>
+        <v>1.662196609686362e-06</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.001011173240840435</v>
+        <v>1.877906242953031e-06</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.00126250647008419</v>
+        <v>9.427807526662946e-06</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.001835796283558011</v>
+        <v>5.006376341043506e-06</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.001095010084100068</v>
+        <v>1.786445636753342e-06</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0001855713489931077</v>
+        <v>4.118943252251484e-06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0008811351144686341</v>
+        <v>1.627785968594253e-05</v>
       </c>
       <c r="BK7" t="n">
-        <v>9.357676754007116e-05</v>
+        <v>5.276932370179566e-06</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0001789161178749055</v>
+        <v>1.831505414884305e-06</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0005401819362305105</v>
+        <v>1.120783144870074e-05</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0003837904951069504</v>
+        <v>1.427272309229011e-06</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0007635062793269753</v>
+        <v>9.298344593844377e-06</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0002460531250108033</v>
+        <v>1.198369591293158e-05</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0002787993289530277</v>
+        <v>8.058177627390251e-07</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0004864093498326838</v>
+        <v>3.869513875542907e-06</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.238225639914162e-05</v>
+        <v>1.172398515336681e-05</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0003813444054685533</v>
+        <v>1.994148533412954e-06</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0003527153166942298</v>
+        <v>1.751962940943486e-06</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.001418260973878205</v>
+        <v>1.742130916682072e-05</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.00019889060058631</v>
+        <v>2.372371000092244e-06</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0001946736301761121</v>
+        <v>7.537474175478565e-06</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0003777304664254189</v>
+        <v>7.218704013212118e-06</v>
       </c>
       <c r="BZ7" t="n">
-        <v>9.601179044693708e-06</v>
+        <v>2.222137482021935e-06</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0001746733614709228</v>
+        <v>3.180678504577372e-06</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0004763617180287838</v>
+        <v>3.759406354220118e-06</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0003450913354754448</v>
+        <v>1.406160890837782e-06</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0001929284480866045</v>
+        <v>3.618451955844648e-06</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0008166501065716147</v>
+        <v>6.444148766604485e-06</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0004272531077731401</v>
+        <v>8.47128035275091e-07</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0004526117700152099</v>
+        <v>1.922444880619878e-06</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0002079127880278975</v>
+        <v>3.72176418750314e-06</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0004358662699814886</v>
+        <v>2.879924977605697e-06</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0001911396975629032</v>
+        <v>2.224313533361055e-07</v>
       </c>
       <c r="CK7" t="n">
-        <v>3.428128911764361e-05</v>
+        <v>6.930637823643337e-07</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0001410286058671772</v>
+        <v>1.308067226091225e-06</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0004147145082242787</v>
+        <v>2.243968992843293e-06</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0001646398304728791</v>
+        <v>2.030841278610751e-05</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0002400665107415989</v>
+        <v>6.366225079545984e-06</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.0003342645359225571</v>
+        <v>8.828700629237574e-06</v>
       </c>
       <c r="CQ7" t="n">
-        <v>5.933157081017271e-05</v>
+        <v>5.179826075618621e-06</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0003390679194126278</v>
+        <v>4.757020633405773e-06</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.000388199114240706</v>
+        <v>6.205843874340644e-07</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0004225945158395916</v>
+        <v>5.335484274837654e-06</v>
       </c>
       <c r="CU7" t="n">
-        <v>4.509499558480456e-05</v>
+        <v>8.110529279292678e-07</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.000132233661133796</v>
+        <v>1.945570147654507e-06</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.0006289189914241433</v>
+        <v>5.892769877391402e-06</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0004380066820885986</v>
+        <v>4.268511020200094e-07</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0006258611101657152</v>
+        <v>2.705866791075096e-06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0001001051714411005</v>
+        <v>2.170046855098917e-06</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.000450568797532469</v>
+        <v>2.24540417548269e-06</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0001857163733802736</v>
+        <v>1.35825439429027e-06</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.000222424219828099</v>
+        <v>1.568230800330639e-06</v>
       </c>
       <c r="DD7" t="n">
-        <v>5.994367529638112e-05</v>
+        <v>2.462066277075792e-06</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0003745141439139843</v>
+        <v>5.86230271437671e-06</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.0007922614458948374</v>
+        <v>2.982542127938359e-06</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0001775588898453861</v>
+        <v>7.127605385903735e-06</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.000628966954536736</v>
+        <v>3.214936668882729e-06</v>
       </c>
       <c r="DI7" t="n">
-        <v>9.028706699609756e-06</v>
+        <v>5.767321908933809e-06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>5.62264394829981e-05</v>
+        <v>4.082774466951378e-06</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.000536660139914602</v>
+        <v>8.288709523185389e-07</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0001204370928462595</v>
+        <v>4.570143573801033e-06</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.0001188980095321313</v>
+        <v>3.633986807471956e-06</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0002031360054388642</v>
+        <v>1.288230805585044e-06</v>
       </c>
       <c r="DO7" t="n">
-        <v>8.227583748521283e-06</v>
+        <v>3.76114621758461e-06</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0005501583218574524</v>
+        <v>2.927041805378394e-06</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0008986341417767107</v>
+        <v>6.067797585274093e-06</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.0001597781665623188</v>
+        <v>2.350823820052028e-07</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0001399182801833376</v>
+        <v>2.431343318676227e-06</v>
       </c>
       <c r="DT7" t="n">
-        <v>1.085067196981981e-06</v>
+        <v>1.217622866533929e-06</v>
       </c>
       <c r="DU7" t="n">
-        <v>3.531140464474447e-05</v>
+        <v>1.308385253651068e-05</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.0002450772153679281</v>
+        <v>4.182006705377717e-07</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0002515431551728398</v>
+        <v>2.482561058059218e-06</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.000141710537718609</v>
+        <v>9.955147106666118e-06</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0009242556407116354</v>
+        <v>9.507879440207034e-06</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0002645978238433599</v>
+        <v>2.460347559463116e-06</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0002430656895739958</v>
+        <v>5.432889793155482e-06</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.060552651528269e-05</v>
+        <v>5.954316293355078e-06</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.190349525539204e-05</v>
+        <v>5.431078534456901e-06</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0001882492942968383</v>
+        <v>1.109450749936514e-05</v>
       </c>
       <c r="EE7" t="n">
-        <v>9.647782280808315e-05</v>
+        <v>8.374407116207294e-06</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0001487289264332503</v>
+        <v>5.930929091846338e-06</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0003212378651369363</v>
+        <v>2.803791858241311e-06</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0001408319221809506</v>
+        <v>3.581964165277896e-07</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0001036640460370108</v>
+        <v>4.514402007771423e-08</v>
       </c>
       <c r="EJ7" t="n">
-        <v>6.393983494490385e-05</v>
+        <v>1.331928046965913e-06</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0002347306435694918</v>
+        <v>4.991591140424134e-06</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.0003203991800546646</v>
+        <v>6.103551868363866e-07</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0001333008549408987</v>
+        <v>4.161110155109782e-06</v>
       </c>
       <c r="EN7" t="n">
-        <v>5.129905184730887e-05</v>
+        <v>1.70038811120321e-06</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0003053874825127423</v>
+        <v>8.637698556412943e-09</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0005265709478408098</v>
+        <v>1.175568968392326e-06</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.0001935545296873897</v>
+        <v>1.08752374217147e-06</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0004107393615413457</v>
+        <v>3.020284111698857e-07</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0005374421598389745</v>
+        <v>6.893564204801805e-06</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0009423760930076241</v>
+        <v>5.018959200242534e-06</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.000338124023983255</v>
+        <v>3.377990424269228e-06</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.0004788956721313298</v>
+        <v>1.284223003494844e-07</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.0001422571367584169</v>
+        <v>2.815025027302909e-06</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0001123208276112564</v>
+        <v>1.977601868929924e-06</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.0006410341011360288</v>
+        <v>8.461022844130639e-06</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0002686849620658904</v>
+        <v>9.164804737338272e-07</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0004563833936117589</v>
+        <v>3.97763324144762e-06</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0001871742715593427</v>
+        <v>2.241861693619285e-06</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.0004752144741360098</v>
+        <v>3.458107130427379e-06</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.000282593973679468</v>
+        <v>3.042786715923285e-07</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0001464868109906092</v>
+        <v>2.537233001476125e-07</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.0002384131366852671</v>
+        <v>2.242437403765507e-06</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0001635726657696068</v>
+        <v>3.789970378420549e-06</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.000383746693842113</v>
+        <v>6.122296269950311e-08</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.000575176440179348</v>
+        <v>3.47343325302063e-06</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.0005547701730392873</v>
+        <v>1.031081592373084e-05</v>
       </c>
       <c r="FK7" t="n">
-        <v>4.767014615936205e-05</v>
+        <v>7.661295967409387e-06</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.0001854507718235254</v>
+        <v>4.135615654377034e-06</v>
       </c>
       <c r="FM7" t="n">
-        <v>3.262590689701028e-05</v>
+        <v>3.960866706620436e-06</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.000215217616641894</v>
+        <v>4.173178240307607e-06</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0002567985211499035</v>
+        <v>1.532327019049262e-06</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0003152037097606808</v>
+        <v>3.74702858607634e-06</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.0001847070961957797</v>
+        <v>2.046494955720846e-06</v>
       </c>
       <c r="FR7" t="n">
-        <v>3.624496821430512e-05</v>
+        <v>8.858231694830465e-07</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.0001160726096713915</v>
+        <v>4.3609807107714e-06</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.001517574302852154</v>
+        <v>2.585933907539584e-05</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0003458997525740415</v>
+        <v>1.603206214895181e-06</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.0002381361555308104</v>
+        <v>1.76392177309026e-07</v>
       </c>
       <c r="FW7" t="n">
-        <v>5.214747216086835e-05</v>
+        <v>3.730799335244228e-06</v>
       </c>
       <c r="FX7" t="n">
-        <v>7.919687777757645e-05</v>
+        <v>2.659627625689609e-06</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.0005082349525764585</v>
+        <v>1.950186288013356e-07</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0003990739351138473</v>
+        <v>3.660333732113941e-06</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.0002504414005670696</v>
+        <v>5.119397883390775e-07</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0003344491124153137</v>
+        <v>1.221290222019888e-05</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0001295205438509583</v>
+        <v>2.312199057996622e-06</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.0004116432392038405</v>
+        <v>1.069057361746673e-06</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.001591982552781701</v>
+        <v>8.611507382738637e-07</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0005640847375616431</v>
+        <v>4.931551302433945e-06</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0002111824869643897</v>
+        <v>6.825294349255273e-06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.003056631190702319</v>
+        <v>0.0003308969899080694</v>
       </c>
       <c r="B8" t="n">
-        <v>0.002407655352726579</v>
+        <v>0.0001098872744478285</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003707921132445335</v>
+        <v>0.002470136387273669</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004515570588409901</v>
+        <v>0.0007946318364702165</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001454193610697985</v>
+        <v>0.0003107279189862311</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001116064959205687</v>
+        <v>0.0002120544668287039</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0005275770090520382</v>
+        <v>0.000263324793195352</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002339033875614405</v>
+        <v>0.001190931303426623</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006316472426988184</v>
+        <v>0.0003620171919465065</v>
       </c>
       <c r="J8" t="n">
-        <v>0.004218565300107002</v>
+        <v>0.0001652503560762852</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002729126019403338</v>
+        <v>9.016090189106762e-06</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002876373939216137</v>
+        <v>0.001843655714765191</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004481079988181591</v>
+        <v>0.0002603402826935053</v>
       </c>
       <c r="N8" t="n">
-        <v>0.001821798738092184</v>
+        <v>0.001142956200055778</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0002525663294363767</v>
+        <v>0.0003069447120651603</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0008574443054385483</v>
+        <v>7.974059553816915e-05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.002348223933950067</v>
+        <v>0.001543710939586163</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0005356139154173434</v>
+        <v>8.75468977028504e-05</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001351801911368966</v>
+        <v>9.843579755397514e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0002467178273946047</v>
+        <v>1.718488056212664e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0001577145303599536</v>
+        <v>0.0006286102579906583</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001648985198698938</v>
+        <v>0.0006291517056524754</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00158423138782382</v>
+        <v>0.0001223397557623684</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0005601029261015356</v>
+        <v>0.0006373132346197963</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0003159969637636095</v>
+        <v>0.000157570349983871</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00248134951107204</v>
+        <v>0.0002094973024213687</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0001331778476014733</v>
+        <v>1.74448432517238e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.302887514815666e-05</v>
+        <v>7.741223089396954e-05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001664615701884031</v>
+        <v>0.0005069967592135072</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.27092527388595e-05</v>
+        <v>0.000822534435428679</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0007583694532513618</v>
+        <v>4.54173277830705e-05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0009686078992672265</v>
+        <v>0.0007228549220599234</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.000315582612529397</v>
+        <v>0.0002044896100414917</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.000459086790215224</v>
+        <v>0.0002276565210195258</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.000718632189091295</v>
+        <v>0.0002954702940769494</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.000387834501452744</v>
+        <v>0.0001676054234849289</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0002927646273747087</v>
+        <v>0.0002530129568185657</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.000733603781554848</v>
+        <v>0.0004314414109103382</v>
       </c>
       <c r="AM8" t="n">
-        <v>6.202310032676905e-05</v>
+        <v>0.000715227797627449</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0005788474809378386</v>
+        <v>0.0008219924056902528</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.411695666320156e-05</v>
+        <v>0.0001281526929233223</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0006255034822970629</v>
+        <v>0.0009133920539170504</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0009091212414205074</v>
+        <v>0.0003745078574866056</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0002451956679578871</v>
+        <v>0.0001957269996637478</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.20348985446617e-05</v>
+        <v>0.0001548916916362941</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0001724029862089083</v>
+        <v>0.0001313456741627306</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0008158014970831573</v>
+        <v>0.001183580374345183</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001962764887139201</v>
+        <v>0.002287165727466345</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.003919837530702353</v>
+        <v>0.001116646686568856</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0007316097617149353</v>
+        <v>0.0013527343980968</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001596036716364324</v>
+        <v>0.001019885414279997</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0007806008798070252</v>
+        <v>0.0007983783143572509</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.002325221430510283</v>
+        <v>0.0003755638317670673</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0007876639720052481</v>
+        <v>6.669991125818342e-05</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.003893561894074082</v>
+        <v>0.0004217027453705668</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.001565909129567444</v>
+        <v>6.36843906249851e-05</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0003718304797075689</v>
+        <v>2.290134580107406e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0006262526148930192</v>
+        <v>0.001275529153645039</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.00301508023403585</v>
+        <v>0.0005388946738094091</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0001092072780011222</v>
+        <v>0.001220632111653686</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.002397224539890885</v>
+        <v>0.0004544361436273903</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.00414732564240694</v>
+        <v>0.000531921221408993</v>
       </c>
       <c r="BK8" t="n">
-        <v>9.285016858484596e-05</v>
+        <v>0.000450801569968462</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0002104879822582006</v>
+        <v>0.0001631193445064127</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0007859623292461038</v>
+        <v>0.0004856601590290666</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001496455166488886</v>
+        <v>0.0003688871511258185</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001222460647113621</v>
+        <v>0.0001125187991419807</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.002064485335722566</v>
+        <v>0.000427340593887493</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0004360888560768217</v>
+        <v>0.0003229602007195354</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0010143315885216</v>
+        <v>0.0001840499171521515</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0006719079683534801</v>
+        <v>9.475629485677928e-05</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0008714803261682391</v>
+        <v>0.0002133587258867919</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0004223606083542109</v>
+        <v>0.0001028507394948974</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001057228771969676</v>
+        <v>0.0003369977057445794</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.001045399461872876</v>
+        <v>0.001255318755283952</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.00157825113274157</v>
+        <v>0.001601632568053901</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0006772530032321811</v>
+        <v>0.0001652940409258008</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0001639558031456545</v>
+        <v>0.0002273867139592767</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0008841666276566684</v>
+        <v>0.0004717029805760831</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.00303935119882226</v>
+        <v>0.0002624971093609929</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.00102838221937418</v>
+        <v>0.0003401324211154133</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0006639238563366234</v>
+        <v>0.0001856411399785429</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0006374602089636028</v>
+        <v>0.0008336646715179086</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0009465898619964719</v>
+        <v>0.0004851570120081306</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0008338429615832865</v>
+        <v>6.614680751226842e-05</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0005319378105923533</v>
+        <v>0.0001229637855431065</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0004727168125100434</v>
+        <v>4.146652645431459e-05</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0005744748050346971</v>
+        <v>4.580472887028009e-05</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0007203768473118544</v>
+        <v>0.0001931673468789086</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0007666764431633055</v>
+        <v>6.277715147007257e-05</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001759448205120862</v>
+        <v>0.0002565372560638934</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0006180766504257917</v>
+        <v>0.0005167718045413494</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.092915772460401e-05</v>
+        <v>0.0003282442630734295</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.000590965268202126</v>
+        <v>0.0008906677248887718</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0004033571167383343</v>
+        <v>0.001260520308278501</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0006380473496392369</v>
+        <v>2.014054916799068e-05</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0004867935203947127</v>
+        <v>0.0003312369808554649</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.001262330333702266</v>
+        <v>4.764915502164513e-05</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0009958542650565505</v>
+        <v>0.001101677771657705</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.000706920400261879</v>
+        <v>0.0002497736422810704</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.00041413409053348</v>
+        <v>0.0005500304396264255</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0004941409570164979</v>
+        <v>0.0004835503059439361</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.000607061549089849</v>
+        <v>0.0001321283343713731</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0004445733793545514</v>
+        <v>4.588692536344752e-05</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0002733468718361109</v>
+        <v>0.0001474229793529958</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0002230076206615195</v>
+        <v>0.0001038093541865237</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0005645189085043967</v>
+        <v>0.0001186521840281785</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.000917041499633342</v>
+        <v>2.770882747427095e-05</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0001755141420289874</v>
+        <v>0.0001880961353890598</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.003237738972529769</v>
+        <v>0.0002149743377231061</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0007703108713030815</v>
+        <v>0.001763040432706475</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.001108673051930964</v>
+        <v>0.0006449295324273407</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001304759411141276</v>
+        <v>0.0007325623882934451</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.002826713025569916</v>
+        <v>0.0002561318106018007</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.003470707684755325</v>
+        <v>0.0003291356260888278</v>
       </c>
       <c r="DL8" t="n">
-        <v>7.487695256713778e-05</v>
+        <v>0.0003905585035681725</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0007565357955172658</v>
+        <v>0.0004124758997932076</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0003096071886830032</v>
+        <v>0.000265378737822175</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0004382555489428341</v>
+        <v>3.016044502146542e-05</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.001313537126407027</v>
+        <v>7.65420263633132e-05</v>
       </c>
       <c r="DQ8" t="n">
-        <v>1.262589648831636e-05</v>
+        <v>0.0002309750416316092</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.001173562370240688</v>
+        <v>0.0004473654553294182</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0002014766359934583</v>
+        <v>3.14700446324423e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0008737503085285425</v>
+        <v>0.0004779063165187836</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0004740615841001272</v>
+        <v>4.302390152588487e-06</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0005387315759435296</v>
+        <v>0.0004204172291792929</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.000313761382130906</v>
+        <v>0.0003455656114965677</v>
       </c>
       <c r="DX8" t="n">
-        <v>9.751955803949386e-05</v>
+        <v>7.434857252519578e-05</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0005775960744358599</v>
+        <v>0.0001197926758322865</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0005660286988131702</v>
+        <v>0.0005614574183709919</v>
       </c>
       <c r="EA8" t="n">
-        <v>5.750946002081037e-05</v>
+        <v>7.107259443728253e-05</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.001589893829077482</v>
+        <v>0.0008810736471787095</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0003979878383688629</v>
+        <v>0.0003425356408115476</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.001552477246150374</v>
+        <v>0.0004965518019162118</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0009945478523150086</v>
+        <v>0.0003929886152036488</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0006121725309640169</v>
+        <v>0.0003167425165884197</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0005497069214470685</v>
+        <v>0.0008050663163885474</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0009139312896877527</v>
+        <v>0.0002907899033743888</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.001198004581965506</v>
+        <v>4.279150743968785e-05</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0001657066895859316</v>
+        <v>0.0004823923227377236</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0004149267915636301</v>
+        <v>0.0001052019506460056</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0004773535183630884</v>
+        <v>6.735820352332667e-05</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0006967423832975328</v>
+        <v>0.0002182414755225182</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.001281339325942099</v>
+        <v>0.0001472489384468645</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0004920762148685753</v>
+        <v>0.0001349519588984549</v>
       </c>
       <c r="EP8" t="n">
-        <v>1.56070600496605e-05</v>
+        <v>0.001109029166400433</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.00105744565371424</v>
+        <v>0.0001119232183555141</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0006679837824776769</v>
+        <v>0.0001519196957815439</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0002217714500147849</v>
+        <v>1.425075970473699e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0001855798182077706</v>
+        <v>0.0008045628201216459</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.000263626454398036</v>
+        <v>8.162058293237351e-06</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.002371425041928887</v>
+        <v>3.786303568631411e-05</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0006622832734137774</v>
+        <v>0.0001004458099487238</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0005811115261167288</v>
+        <v>0.000198889640159905</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0005172282690182328</v>
+        <v>0.0008021839894354343</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.0008175960392691195</v>
+        <v>0.0004470228159334511</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0006666056578978896</v>
+        <v>4.413002170622349e-05</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0003371754137333483</v>
+        <v>4.566156712826341e-05</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0004862587666139007</v>
+        <v>0.0002219850430265069</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0003331667103338987</v>
+        <v>0.0001121040986618027</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.000599715334828943</v>
+        <v>4.13568013755139e-05</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.001029135892167687</v>
+        <v>9.930081432685256e-05</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0001822594058467075</v>
+        <v>2.415975177427754e-05</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0003790936898440123</v>
+        <v>0.0002707465027924627</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.0002482401323504746</v>
+        <v>0.0009944449411705136</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.001244991668500006</v>
+        <v>0.0004895314341410995</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0009045028127729893</v>
+        <v>0.0005851125461049378</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0006267534918151796</v>
+        <v>0.0007762045715935528</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0006474852561950684</v>
+        <v>0.0001034897868521512</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0005739645566791296</v>
+        <v>0.0004496578476391733</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.001464909873902798</v>
+        <v>0.0002470511826686561</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.001983435591682792</v>
+        <v>0.0006190717103891075</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.001273459522053599</v>
+        <v>0.0001811074616853148</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.002605878980830312</v>
+        <v>0.0009017406264320016</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.001184012973681092</v>
+        <v>0.0002349740680074319</v>
       </c>
       <c r="FT8" t="n">
-        <v>5.317290197126567e-05</v>
+        <v>0.001525699044577777</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.001415548147633672</v>
+        <v>0.0001377895241603255</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.0003511732793413103</v>
+        <v>0.0006040576263330877</v>
       </c>
       <c r="FW8" t="n">
-        <v>7.898441981524229e-05</v>
+        <v>0.001205301028676331</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.001084763556718826</v>
+        <v>0.0008368940907530487</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.0006120681064203382</v>
+        <v>0.0001998863735934719</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0003602886572480202</v>
+        <v>0.000918346515391022</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0009957391303032637</v>
+        <v>0.0009040714940056205</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0007914906018413603</v>
+        <v>0.0001134644262492657</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.002109637018293142</v>
+        <v>0.0005530923954211175</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.001558388117700815</v>
+        <v>0.0002446817816235125</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.0002844712871592492</v>
+        <v>0.0001412840647390112</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.000796083128079772</v>
+        <v>0.0002959485864266753</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0004328575450927019</v>
+        <v>1.000858173938468e-05</v>
       </c>
     </row>
     <row r="9">
@@ -5551,3416 +5551,3416 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.001191097544506192</v>
+        <v>7.28693266864866e-05</v>
       </c>
       <c r="B10" t="n">
-        <v>0.05022741109132767</v>
+        <v>0.0005555892130360007</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00569301750510931</v>
+        <v>2.21463487832807e-05</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01582968607544899</v>
+        <v>0.0001096593841793947</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04025068879127502</v>
+        <v>4.760586307384074e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0152417179197073</v>
+        <v>0.0004141800454817712</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0029085548594594</v>
+        <v>0.0001726319169392809</v>
       </c>
       <c r="H10" t="n">
-        <v>0.005975112318992615</v>
+        <v>0.0002071916533168405</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004133351147174835</v>
+        <v>7.646620360901579e-06</v>
       </c>
       <c r="J10" t="n">
-        <v>0.003509336151182652</v>
+        <v>6.013375241309404e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03605338558554649</v>
+        <v>0.0006905116024427116</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003501357277855277</v>
+        <v>9.148269600700587e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>0.005464003421366215</v>
+        <v>0.0002490127517376095</v>
       </c>
       <c r="N10" t="n">
-        <v>0.03433801233768463</v>
+        <v>0.0001922472292790189</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01452561840415001</v>
+        <v>0.0004524299583863467</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0004223831929266453</v>
+        <v>3.82636790163815e-06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.006289922632277012</v>
+        <v>1.73589214682579e-05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00098752835765481</v>
+        <v>0.0002196144632762298</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0001753409160301089</v>
+        <v>3.541193109413143e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.009287414140999317</v>
+        <v>7.54330976633355e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>0.001808846718631685</v>
+        <v>4.588152660289779e-05</v>
       </c>
       <c r="V10" t="n">
-        <v>0.006424360908567905</v>
+        <v>0.0001020225099637173</v>
       </c>
       <c r="W10" t="n">
-        <v>0.009153062477707863</v>
+        <v>2.015855898207519e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>0.006686713546514511</v>
+        <v>4.837982851313427e-05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.003084121039137244</v>
+        <v>5.758667612099089e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.008944260887801647</v>
+        <v>8.362685184692964e-05</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001229018205776811</v>
+        <v>6.051682066754438e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.001785463653504848</v>
+        <v>4.680307029047981e-05</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.005678755231201649</v>
+        <v>3.714988997671753e-05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0006164159858599305</v>
+        <v>2.752881664491724e-05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0001539934310130775</v>
+        <v>9.106345532927662e-05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.007463855668902397</v>
+        <v>0.0002029061724897474</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0009404115262441337</v>
+        <v>0.0002892256597988307</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.008253248408436775</v>
+        <v>1.240900201082695e-05</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0007175393984653056</v>
+        <v>0.0003326375735923648</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0002720064949244261</v>
+        <v>5.682775008608587e-05</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.007909615524113178</v>
+        <v>1.243424594576936e-05</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.008449370041489601</v>
+        <v>7.255682430695742e-05</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.003110982710495591</v>
+        <v>8.857154898578301e-05</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.001451031304895878</v>
+        <v>4.14370369981043e-05</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.00514703057706356</v>
+        <v>9.768649033503607e-05</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.006989204324781895</v>
+        <v>6.51169175398536e-05</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.003965099807828665</v>
+        <v>9.608633263269439e-05</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0003987922973465174</v>
+        <v>0.0001657397660892457</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.003911431413143873</v>
+        <v>2.396414129179902e-05</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.007175976410508156</v>
+        <v>8.464018173981458e-05</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.04658491164445877</v>
+        <v>0.0006031186203472316</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.005339469760656357</v>
+        <v>0.0001446496025891975</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.002844769973307848</v>
+        <v>7.883296348154545e-05</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.007432444486767054</v>
+        <v>0.0002988100168295205</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.01590982265770435</v>
+        <v>0.0004240903945174068</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.003975765779614449</v>
+        <v>1.733001045067795e-05</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.01160833891481161</v>
+        <v>9.573839633958414e-06</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.002475731074810028</v>
+        <v>5.123280425323173e-05</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.002853062469512224</v>
+        <v>5.797141966468189e-07</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.009313090704381466</v>
+        <v>1.649434852879494e-05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.005738446488976479</v>
+        <v>5.705520015908405e-05</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0042923828586936</v>
+        <v>5.241885810391977e-05</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.02891380712389946</v>
+        <v>8.760606579016894e-05</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.006681757979094982</v>
+        <v>6.47144770482555e-06</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.00206645904108882</v>
+        <v>6.412432412616909e-05</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.01261517684906721</v>
+        <v>0.0001666306343395263</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.005011040717363358</v>
+        <v>1.921532202686649e-05</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.006030167918652296</v>
+        <v>2.327227412024513e-05</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.02485455013811588</v>
+        <v>0.000165102508617565</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.005739502143114805</v>
+        <v>3.171535354340449e-07</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.00743191409856081</v>
+        <v>2.796696207951754e-06</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.01384090725332499</v>
+        <v>0.0001691940851742402</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.007132110185921192</v>
+        <v>0.0001025969977490604</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.005719494540244341</v>
+        <v>0.000192642561160028</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.003184293862432241</v>
+        <v>4.285661270841956e-05</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0003595222369767725</v>
+        <v>0.0001789437956176698</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.005570964887738228</v>
+        <v>2.818828215822577e-05</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.02571358904242516</v>
+        <v>0.0003573461435735226</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.01158741209656</v>
+        <v>4.777596041094512e-05</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0009675708133727312</v>
+        <v>0.0001488142879679799</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.007063476368784904</v>
+        <v>8.737506504985504e-07</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.004646376706659794</v>
+        <v>0.0001627183810342103</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.006346370093524456</v>
+        <v>8.946192247094586e-05</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.002861106535419822</v>
+        <v>6.639792991336435e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.000342022511176765</v>
+        <v>6.913259858265519e-05</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.00213120155967772</v>
+        <v>1.292228898819303e-05</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.008271962404251099</v>
+        <v>0.0001712192170089111</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.002280310494825244</v>
+        <v>2.942786977655487e-06</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.004655108321458101</v>
+        <v>5.484576831804588e-06</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.003812854643911123</v>
+        <v>4.475945388549007e-06</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.003491690382361412</v>
+        <v>0.0001012208085739985</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.004409048706293106</v>
+        <v>3.206379187759012e-05</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.001025179750286043</v>
+        <v>5.399162910180166e-05</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0008560515707358718</v>
+        <v>6.970870163058862e-05</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.01618483290076256</v>
+        <v>9.731897443998605e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.01170648075640202</v>
+        <v>0.0002623783657327294</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.001628346741199493</v>
+        <v>0.0001896939793368801</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.004874995909631252</v>
+        <v>0.0001313083485001698</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.00666422862559557</v>
+        <v>2.711515480768867e-05</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.003830478526651859</v>
+        <v>2.599434446892701e-05</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.00245998241007328</v>
+        <v>8.639731095172465e-05</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.003475156147032976</v>
+        <v>3.366488090250641e-05</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.004036528058350086</v>
+        <v>0.0001220832928083837</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.00168539653532207</v>
+        <v>2.248970849905163e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.005375133827328682</v>
+        <v>0.0001600115501787513</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.003376675304025412</v>
+        <v>1.885858000605367e-05</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.007598419208079576</v>
+        <v>1.825687650125474e-05</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.002533584134653211</v>
+        <v>3.866825863951817e-06</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.004627473652362823</v>
+        <v>0.0001130587697844021</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.004192303866147995</v>
+        <v>1.592893386259675e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.002671852707862854</v>
+        <v>6.094069976825267e-05</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0001382086047669873</v>
+        <v>5.512370989890769e-05</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.004616300109773874</v>
+        <v>5.012449764763005e-05</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.01387617364525795</v>
+        <v>0.0002027837908826768</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.00204988825134933</v>
+        <v>6.828219920862466e-05</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0259917676448822</v>
+        <v>2.474720531608909e-06</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.008478599600493908</v>
+        <v>0.0001284733152715489</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.003122009802609682</v>
+        <v>0.000132409404614009</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.01312390714883804</v>
+        <v>4.039282066514716e-05</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.005792370066046715</v>
+        <v>7.96399253886193e-05</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.006392334122210741</v>
+        <v>1.032471482176334e-05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.004693895578384399</v>
+        <v>0.0001073230596375652</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.004723917692899704</v>
+        <v>9.353068890050054e-05</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.006087255664169788</v>
+        <v>6.279176159296185e-05</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.002180346753448248</v>
+        <v>0.0001588269806234166</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.005106090568006039</v>
+        <v>2.128627602360211e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.00502646854147315</v>
+        <v>7.685260789003223e-05</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.0007240955019369721</v>
+        <v>5.783428787253797e-05</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.004234307911247015</v>
+        <v>7.231528434203938e-05</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.001223999890498817</v>
+        <v>6.641286017838866e-05</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.004883380141109228</v>
+        <v>8.30512581160292e-05</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.002487133257091045</v>
+        <v>2.549175042076968e-05</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.001220733858644962</v>
+        <v>7.669294427614659e-05</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.005202278960496187</v>
+        <v>1.904466989799403e-05</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.004564573056995869</v>
+        <v>1.994594094867352e-05</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0009920235024765134</v>
+        <v>8.92945536179468e-06</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.003548392094671726</v>
+        <v>5.003823025617748e-05</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0008111021597869694</v>
+        <v>0.0001537683128844947</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0009814588120207191</v>
+        <v>0.000153328146552667</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.003456946695223451</v>
+        <v>1.175994839286432e-07</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.002605551620945334</v>
+        <v>4.728083877125755e-05</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.001666992902755737</v>
+        <v>6.639037746936083e-05</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.002913523931056261</v>
+        <v>9.499397856416181e-05</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.004035132471472025</v>
+        <v>3.195037061232142e-05</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0006597572937607765</v>
+        <v>4.694856761489064e-05</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.005313134752213955</v>
+        <v>1.156082726083696e-05</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.001293791690841317</v>
+        <v>1.546667590446305e-05</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0003392671351321042</v>
+        <v>2.932189090643078e-06</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.008019153028726578</v>
+        <v>7.865397492423654e-06</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.00330646988004446</v>
+        <v>8.775694004725665e-05</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.00581539049744606</v>
+        <v>4.832130798604339e-05</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.007054667454212904</v>
+        <v>6.986258085817099e-05</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0003086437936872244</v>
+        <v>0.0001337477588094771</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.009754768572747707</v>
+        <v>0.0001085918920580298</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.004062202759087086</v>
+        <v>5.574784154305235e-07</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.00579201802611351</v>
+        <v>3.682752867462113e-05</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.001101154601201415</v>
+        <v>1.96845594473416e-05</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.001947366166859865</v>
+        <v>8.135248208418489e-08</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.003628987120464444</v>
+        <v>0.0002092413633363321</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.001666106632910669</v>
+        <v>3.152792487526312e-06</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.005546715576201677</v>
+        <v>3.007913073815871e-05</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.003020909382030368</v>
+        <v>1.388380678690737e-05</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.005166373215615749</v>
+        <v>7.613238994963467e-05</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.005687486380338669</v>
+        <v>2.930400660261512e-05</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.001603060169145465</v>
+        <v>4.338336657383479e-05</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.002533058635890484</v>
+        <v>8.954923941928428e-06</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.003515624441206455</v>
+        <v>2.695906187000219e-05</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.006959089543670416</v>
+        <v>0.0001696658000582829</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.004185901954770088</v>
+        <v>0.0001234547817148268</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.006990125868469477</v>
+        <v>0.000129816951812245</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.003811903297901154</v>
+        <v>7.332922541536391e-05</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.001603489508852363</v>
+        <v>0.0001934825850185007</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.003517996752634645</v>
+        <v>6.06868343311362e-05</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.002697983058169484</v>
+        <v>7.729101344011724e-05</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.003209811635315418</v>
+        <v>0.0002853247860912234</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.01259953528642654</v>
+        <v>3.03020715364255e-05</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.002455375157296658</v>
+        <v>9.172006684821099e-05</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.003419060725718737</v>
+        <v>0.0002444419951643795</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.01282912772148848</v>
+        <v>9.724874689709395e-05</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.008010441437363625</v>
+        <v>0.0001195066361106001</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.002363457344472408</v>
+        <v>3.75282543245703e-05</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.003259680001065135</v>
+        <v>3.767782618524507e-05</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.001897281152196229</v>
+        <v>0.0002782395167741925</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.002100622514262795</v>
+        <v>4.755113332066685e-05</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.01071579940617085</v>
+        <v>6.304254930000752e-05</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.006224635522812605</v>
+        <v>1.238681034010369e-05</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.002098040422424674</v>
+        <v>0.0001041301438817754</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.001188652357086539</v>
+        <v>6.706000567646697e-05</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.002821685746312141</v>
+        <v>0.00021988051594235</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.006729810498654842</v>
+        <v>0.0002190435479860753</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.01353388279676437</v>
+        <v>5.346409307094291e-05</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.004357235971838236</v>
+        <v>5.630091254715808e-05</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.002679110504686832</v>
+        <v>2.74867797998013e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.001377147738821805</v>
+        <v>0.0545811653137207</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02880252338945866</v>
+        <v>0.2489801347255707</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00426807813346386</v>
+        <v>0.03457757830619812</v>
       </c>
       <c r="D11" t="n">
-        <v>0.02013137377798557</v>
+        <v>0.1140885502099991</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008319368585944176</v>
+        <v>0.06146321445703506</v>
       </c>
       <c r="F11" t="n">
-        <v>0.004228109493851662</v>
+        <v>0.05439512804150581</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005154773592948914</v>
+        <v>0.07186031341552734</v>
       </c>
       <c r="H11" t="n">
-        <v>0.002369419671595097</v>
+        <v>0.05041780322790146</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0005113924853503704</v>
+        <v>0.01908118650317192</v>
       </c>
       <c r="J11" t="n">
-        <v>0.004867265932261944</v>
+        <v>0.01404648646712303</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0216892845928669</v>
+        <v>0.2547723054885864</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00116914149839431</v>
+        <v>0.03901589661836624</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01902243867516518</v>
+        <v>0.1512376666069031</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01171044167131186</v>
+        <v>0.0961616039276123</v>
       </c>
       <c r="O11" t="n">
-        <v>0.008774730376899242</v>
+        <v>0.02637415006756783</v>
       </c>
       <c r="P11" t="n">
-        <v>0.002680010395124555</v>
+        <v>0.06919480115175247</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.002836399944499135</v>
+        <v>0.01128812041133642</v>
       </c>
       <c r="R11" t="n">
-        <v>0.003518176730722189</v>
+        <v>0.03031420893967152</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001643724273890257</v>
+        <v>0.0127076543867588</v>
       </c>
       <c r="T11" t="n">
-        <v>0.006240048445761204</v>
+        <v>0.04033727571368217</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0003720565291587263</v>
+        <v>0.01507102698087692</v>
       </c>
       <c r="V11" t="n">
-        <v>0.002560003893449903</v>
+        <v>0.02559168636798859</v>
       </c>
       <c r="W11" t="n">
-        <v>0.001342018134891987</v>
+        <v>0.02629570849239826</v>
       </c>
       <c r="X11" t="n">
-        <v>0.004954779986292124</v>
+        <v>0.0429038405418396</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.004048265982419252</v>
+        <v>0.01193073391914368</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.001676858635619283</v>
+        <v>0.02403915859758854</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.003120661247521639</v>
+        <v>0.04256740212440491</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001232220092788339</v>
+        <v>0.03642374649643898</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.005270405672490597</v>
+        <v>0.01077990047633648</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.001281871926039457</v>
+        <v>0.02168105728924274</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.00151310081128031</v>
+        <v>0.07031437009572983</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.001279339892789721</v>
+        <v>0.06475645303726196</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.000521081208717078</v>
+        <v>0.04928945749998093</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.00306396558880806</v>
+        <v>0.02421991713345051</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.002818779088556767</v>
+        <v>0.0105894673615694</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.00108483072835952</v>
+        <v>0.01962964981794357</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.002054616110399365</v>
+        <v>0.004330573603510857</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.004504616837948561</v>
+        <v>0.09069041907787323</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0005180586013011634</v>
+        <v>0.009007321670651436</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.642948862165213e-05</v>
+        <v>0.04702148586511612</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.001652408740483224</v>
+        <v>0.03957237303256989</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.001824974548071623</v>
+        <v>0.03807207942008972</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.002846044953912497</v>
+        <v>0.01330146938562393</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.002109558321535587</v>
+        <v>0.003930696286261082</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.001742572174407542</v>
+        <v>0.003524000756442547</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.002867016708478332</v>
+        <v>0.01719985902309418</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.02026291377842426</v>
+        <v>0.1607261002063751</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.001333304913714528</v>
+        <v>0.007294912822544575</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.004060921724885702</v>
+        <v>0.03706187754869461</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0003750950563699007</v>
+        <v>0.1131021454930305</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.0004084339598193765</v>
+        <v>0.02239338122308254</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.004069700371474028</v>
+        <v>0.01267042942345142</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.001865547732450068</v>
+        <v>0.02622687257826328</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0003527198859956115</v>
+        <v>0.01002236176282167</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.00061378488317132</v>
+        <v>0.04984972253441811</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.003865828271955252</v>
+        <v>0.003798876889050007</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.006112862844020128</v>
+        <v>0.03818845003843307</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.00625288300216198</v>
+        <v>0.03172142803668976</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.01140810083597898</v>
+        <v>0.02762655727565289</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.002558227861300111</v>
+        <v>0.01644759997725487</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.002293575089424849</v>
+        <v>0.01476436108350754</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.002489244332537055</v>
+        <v>0.03507504612207413</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.002398841315880418</v>
+        <v>0.03337445110082626</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.002869765507057309</v>
+        <v>0.003815636737272143</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.003750015515834093</v>
+        <v>0.02058935537934303</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.002974541857838631</v>
+        <v>0.007297275587916374</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.001271262066438794</v>
+        <v>0.00863095186650753</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.00201986194588244</v>
+        <v>0.02816122025251389</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.002943632658571005</v>
+        <v>0.002562725683674216</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0002484165597707033</v>
+        <v>0.00968010351061821</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0008999648271128535</v>
+        <v>0.001518624136224389</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.002286524279043078</v>
+        <v>0.007359581999480724</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.002240911591798067</v>
+        <v>0.0315113291144371</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.01074874028563499</v>
+        <v>0.1424535512924194</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.004578945226967335</v>
+        <v>0.0009003146551549435</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.004279681015759706</v>
+        <v>0.05917319282889366</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.774857603071723e-05</v>
+        <v>0.03026171214878559</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.001340351765975356</v>
+        <v>0.05461336299777031</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.002529368503019214</v>
+        <v>0.02848034724593163</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.000513292383402586</v>
+        <v>0.009270183742046356</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.002494310727342963</v>
+        <v>0.03921740129590034</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.000729358522221446</v>
+        <v>0.01368368044495583</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.004997002892196178</v>
+        <v>0.07536458969116211</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.002429214771836996</v>
+        <v>0.0183323360979557</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.002374211559072137</v>
+        <v>0.04812893271446228</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0008195573464035988</v>
+        <v>0.0117879007011652</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.002099745674058795</v>
+        <v>0.0103667238727212</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0008370574214495718</v>
+        <v>0.001757047139108181</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0003222997765988111</v>
+        <v>0.009289967827498913</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.00144670985173434</v>
+        <v>0.008291058242321014</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.005227241199463606</v>
+        <v>0.01391836442053318</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.002271206583827734</v>
+        <v>0.09726525843143463</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0001397784217260778</v>
+        <v>0.03765525296330452</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.002693971851840615</v>
+        <v>0.1140984743833542</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.003411797573789954</v>
+        <v>0.06563925743103027</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.000819746870547533</v>
+        <v>0.02085519023239613</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.003281159792095423</v>
+        <v>0.01464405097067356</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.003388659795746207</v>
+        <v>0.0004389476962387562</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0002024001005338505</v>
+        <v>0.0265057161450386</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0005906772566959262</v>
+        <v>0.007774531841278076</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.004481275100260973</v>
+        <v>0.06947663426399231</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.002719469135627151</v>
+        <v>0.01590491086244583</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.003193331882357597</v>
+        <v>0.0495322085916996</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0009766261791810393</v>
+        <v>0.01940443366765976</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.00311803468503058</v>
+        <v>0.006917987484484911</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.001058090012520552</v>
+        <v>0.007106698583811522</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0007218342507258058</v>
+        <v>0.009029289707541466</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0004359603626653552</v>
+        <v>0.01208449807018042</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.001791298622265458</v>
+        <v>0.01828954182565212</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.00516132777556777</v>
+        <v>0.07384692132472992</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0005762525252066553</v>
+        <v>0.0391678512096405</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.006731047760695219</v>
+        <v>0.04455879330635071</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0006998047465458512</v>
+        <v>0.04044367745518684</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.003321409691125154</v>
+        <v>0.06450642645359039</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.001311637926846743</v>
+        <v>0.01991893723607063</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0001616369117982686</v>
+        <v>0.05431550741195679</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.001112288446165621</v>
+        <v>0.03930649906396866</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.000120419732411392</v>
+        <v>0.0355435386300087</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0008948829490691423</v>
+        <v>0.05182212591171265</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.001074239728040993</v>
+        <v>0.006203903816640377</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0001667148317210376</v>
+        <v>0.01919351518154144</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.00252835126593709</v>
+        <v>0.009477226994931698</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.00150637177284807</v>
+        <v>0.006545602343976498</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.002328572794795036</v>
+        <v>0.01088842749595642</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.002051047747954726</v>
+        <v>0.04304467886686325</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.003398660337552428</v>
+        <v>0.06361868232488632</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.000363012426532805</v>
+        <v>0.02698289230465889</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.002225070726126432</v>
+        <v>0.009949397295713425</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.003210053779184818</v>
+        <v>0.01585670746862888</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.001864886842668056</v>
+        <v>0.01285106875002384</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.001916900160722435</v>
+        <v>0.001388439908623695</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.0006442611338570714</v>
+        <v>0.03707524016499519</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.001497913850471377</v>
+        <v>0.007790999487042427</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.001430845353752375</v>
+        <v>0.08262183517217636</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.002505285432562232</v>
+        <v>0.05059655755758286</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0001992594916373491</v>
+        <v>0.01264585461467505</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.002536965534090996</v>
+        <v>0.06531417369842529</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.002480914816260338</v>
+        <v>0.007405541837215424</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.00295161223039031</v>
+        <v>0.03191287443041801</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.001121455570682883</v>
+        <v>0.01810118369758129</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.004172113724052906</v>
+        <v>0.009652049280703068</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0006773144705221057</v>
+        <v>0.0009267665445804596</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.0005692739505320787</v>
+        <v>0.009883219376206398</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0006409372435882688</v>
+        <v>0.007868977263569832</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.0001064419047906995</v>
+        <v>0.003183237044140697</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.003990615718066692</v>
+        <v>0.05170837044715881</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.003247925546020269</v>
+        <v>0.009648327715694904</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.001103017013520002</v>
+        <v>0.03396954387426376</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.001413306803442538</v>
+        <v>0.004539173562079668</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.002804652322083712</v>
+        <v>0.00707688182592392</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.001906120916828513</v>
+        <v>0.01718658395111561</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.002914446173235774</v>
+        <v>0.0207029078155756</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0001261269499082118</v>
+        <v>0.03032818809151649</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0001898101763799787</v>
+        <v>0.01874410733580589</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.004653595387935638</v>
+        <v>0.08357012271881104</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.001724513480439782</v>
+        <v>0.01555190235376358</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.003504339372739196</v>
+        <v>0.05238280445337296</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0009158588945865631</v>
+        <v>0.01244270801544189</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.002743775025010109</v>
+        <v>0.01715516671538353</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.00100486190058291</v>
+        <v>0.007841247133910656</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.0004280986613593996</v>
+        <v>0.01474249828606844</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.001263132318854332</v>
+        <v>0.0154232494533062</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0006651327712461352</v>
+        <v>0.008106216788291931</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.001839426928199828</v>
+        <v>0.03108372166752815</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.002628092421218753</v>
+        <v>0.02593991532921791</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.002424519043415785</v>
+        <v>0.03376874700188637</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0005027049919590354</v>
+        <v>0.0002766516990959644</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.002871349453926086</v>
+        <v>0.01819381862878799</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.000483688956592232</v>
+        <v>0.001606462523341179</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0007408355013467371</v>
+        <v>0.005392041057348251</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0004945837426930666</v>
+        <v>0.03264981508255005</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.000412993598729372</v>
+        <v>0.02846275642514229</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.004289727658033371</v>
+        <v>0.03635043650865555</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.002542817266657948</v>
+        <v>0.0224822498857975</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.003871506080031395</v>
+        <v>0.03890106081962585</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.001747166039422154</v>
+        <v>0.02380293793976307</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.002655002987012267</v>
+        <v>0.0001950263977050781</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.001766979694366455</v>
+        <v>0.02392776682972908</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.0008292146376334131</v>
+        <v>0.03208582475781441</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.001492640934884548</v>
+        <v>0.03502598777413368</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.005116486921906471</v>
+        <v>0.04622571170330048</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0008319296757690609</v>
+        <v>0.0691949799656868</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0002839644148480147</v>
+        <v>0.0152294710278511</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.000693475129082799</v>
+        <v>0.02185056731104851</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.002016171114519238</v>
+        <v>0.05901509150862694</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.002217236906290054</v>
+        <v>0.03223265707492828</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.01146338880062103</v>
+        <v>0.0484558567404747</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0005066328449174762</v>
+        <v>0.02162284404039383</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.002989727770909667</v>
+        <v>0.006251801736652851</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0002017038059420884</v>
+        <v>0.0001013203000184149</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001775491167791188</v>
+        <v>0.00108284002635628</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001180557446787134</v>
+        <v>0.0002647373767104</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001041261944919825</v>
+        <v>0.0002053713978966698</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0001610228209756315</v>
+        <v>2.129151107510552e-05</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001284115947782993</v>
+        <v>0.0003836914256680757</v>
       </c>
       <c r="G12" t="n">
-        <v>0.000103134945675265</v>
+        <v>2.005538954108488e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0004323855973780155</v>
+        <v>9.965622302843258e-05</v>
       </c>
       <c r="I12" t="n">
-        <v>8.424340921919793e-05</v>
+        <v>0.0002249059907626361</v>
       </c>
       <c r="J12" t="n">
-        <v>0.000333071657223627</v>
+        <v>1.009188417810947e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.001433245721273124</v>
+        <v>0.001443683984689415</v>
       </c>
       <c r="L12" t="n">
-        <v>8.929199975682423e-05</v>
+        <v>0.0002730556589085609</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0009446812327951193</v>
+        <v>0.0003468048817012459</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0001965010451385751</v>
+        <v>0.0002431953907944262</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001373364240862429</v>
+        <v>0.0003563241916708648</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0001514260220574215</v>
+        <v>0.0003237586643081158</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.373498424887657e-05</v>
+        <v>0.0004555565537884831</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0001118366562877782</v>
+        <v>0.0003041839227080345</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0001075441177817993</v>
+        <v>0.0002021621621679515</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0003610547573771328</v>
+        <v>0.0002491419145371765</v>
       </c>
       <c r="U12" t="n">
-        <v>1.111364144890103e-05</v>
+        <v>8.886737487046048e-05</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0002733987639658153</v>
+        <v>0.0001857807656051591</v>
       </c>
       <c r="W12" t="n">
-        <v>6.978478631936014e-05</v>
+        <v>7.288322376552969e-05</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0001721120206639171</v>
+        <v>2.521077658457216e-05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0001749326474964619</v>
+        <v>0.0001201339982799254</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.958249049494043e-05</v>
+        <v>0.000320793449645862</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0001969561562873423</v>
+        <v>5.758499901276082e-05</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.426583134569228e-05</v>
+        <v>0.0002546423929743469</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.0002910417970269918</v>
+        <v>1.316119232797064e-05</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.042563887196593e-05</v>
+        <v>6.626501999562606e-05</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0001714204263407737</v>
+        <v>0.0001359242596663535</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0001924647367559373</v>
+        <v>0.000696411996614188</v>
       </c>
       <c r="AG12" t="n">
-        <v>8.098444232018664e-05</v>
+        <v>7.738727435935289e-05</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0003262722748331726</v>
+        <v>0.0001335074339294806</v>
       </c>
       <c r="AI12" t="n">
-        <v>7.771306263748556e-05</v>
+        <v>0.0001963887480087578</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0001069562931661494</v>
+        <v>0.0001216956443386152</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0002633408585097641</v>
+        <v>0.0001005289959721267</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0002870156604330987</v>
+        <v>9.173875150736421e-05</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.206080120638944e-05</v>
+        <v>2.655512616911437e-05</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.181108230724931e-05</v>
+        <v>0.0002271217381348833</v>
       </c>
       <c r="AO12" t="n">
-        <v>9.441659494768828e-05</v>
+        <v>8.309613622259349e-05</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0002581598237156868</v>
+        <v>3.533851486281492e-05</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0001303475437453017</v>
+        <v>0.0002331754221813753</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.081069972831756e-05</v>
+        <v>0.0003138013125862926</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0002106672618538141</v>
+        <v>9.99329931801185e-05</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0002344698878005147</v>
+        <v>0.0001245421735802665</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.001335881883278489</v>
+        <v>0.001073422958143055</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.202950756531209e-05</v>
+        <v>5.448658339446411e-05</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.007437019026838e-05</v>
+        <v>6.331814802251756e-05</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.641388371353969e-05</v>
+        <v>0.0003483537293504924</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0008030689205043018</v>
+        <v>0.000265278504230082</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.0001752924872562289</v>
+        <v>2.2319483832689e-05</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0004834872670471668</v>
+        <v>0.0001737257844069973</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.0003064424090553075</v>
+        <v>0.0001088798162527382</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.0001280210562981665</v>
+        <v>3.887447383021936e-05</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0003415225946810097</v>
+        <v>0.0001135932907345705</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0004274866078048944</v>
+        <v>9.586854139342904e-05</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0003943828633055091</v>
+        <v>0.0001532131864223629</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.0004239728441461921</v>
+        <v>0.0001694077800493687</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0003133608843199909</v>
+        <v>1.73178777913563e-05</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.433394936611876e-05</v>
+        <v>0.0001167628288385458</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.0005771802389062941</v>
+        <v>0.0001055152461049147</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.837390300352126e-05</v>
+        <v>0.0001087151904357597</v>
       </c>
       <c r="BL12" t="n">
-        <v>2.214116102550179e-05</v>
+        <v>0.0001449228002456948</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0004751275409944355</v>
+        <v>0.0001512046583229676</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0002408674481557682</v>
+        <v>9.613150905352086e-05</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0003328528255224228</v>
+        <v>0.000106335268355906</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0004245591117069125</v>
+        <v>0.0001723450550343841</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0001160372121375985</v>
+        <v>9.949653758667409e-06</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.0003260452067479491</v>
+        <v>0.0002710733679123223</v>
       </c>
       <c r="BS12" t="n">
-        <v>6.972344272071496e-05</v>
+        <v>2.732385109993629e-05</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.0001731711381580681</v>
+        <v>0.0001239105622516945</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0001192156778415665</v>
+        <v>0.0002116672549163923</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0006742916302755475</v>
+        <v>0.0007706833421252668</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0002426957216812298</v>
+        <v>1.934278952830937e-05</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.0001154033961938694</v>
+        <v>0.000295643083518371</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0001763844338711351</v>
+        <v>8.725458610570058e-05</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.0002050506882369518</v>
+        <v>4.068981797900051e-05</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0003186464309692383</v>
+        <v>0.0001134168851422146</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0002213718253187835</v>
+        <v>5.598668212769553e-05</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.000169859456946142</v>
+        <v>1.016191527014598e-05</v>
       </c>
       <c r="CD12" t="n">
-        <v>1.32856730488129e-05</v>
+        <v>0.0001317628775723279</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0003410179051570594</v>
+        <v>0.000283050088910386</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.0001781032333383337</v>
+        <v>6.449396460084245e-05</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0002261996269226074</v>
+        <v>6.688873691018671e-05</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0001691784564172849</v>
+        <v>2.958469303848688e-05</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0001997137587750331</v>
+        <v>0.0001138787774834782</v>
       </c>
       <c r="CJ12" t="n">
-        <v>6.608777039218694e-05</v>
+        <v>8.308118412969634e-05</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.0001052821971825324</v>
+        <v>1.476381657994352e-05</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0001236710086232051</v>
+        <v>1.626223638595548e-05</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0004235236265230924</v>
+        <v>6.36338081676513e-05</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0003294147027190775</v>
+        <v>0.0007451673154719174</v>
       </c>
       <c r="CO12" t="n">
-        <v>5.191349555389024e-05</v>
+        <v>4.985453051631339e-05</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.0002652661933097988</v>
+        <v>0.0002839071967173368</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0001844995422288775</v>
+        <v>0.0001936621556524187</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.0001718136190902442</v>
+        <v>1.185247765533859e-05</v>
       </c>
       <c r="CS12" t="n">
-        <v>6.197795300977305e-05</v>
+        <v>4.617208469426259e-05</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0001931748702190816</v>
+        <v>4.897277540294454e-05</v>
       </c>
       <c r="CU12" t="n">
-        <v>6.517017754958943e-05</v>
+        <v>3.282535908510908e-05</v>
       </c>
       <c r="CV12" t="n">
-        <v>3.301556353108026e-05</v>
+        <v>8.875149069353938e-05</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0002919123216997832</v>
+        <v>0.0003023507015313953</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0001943569222930819</v>
+        <v>5.573774615186267e-05</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.000319199520163238</v>
+        <v>6.064930857974105e-05</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0001340393209829926</v>
+        <v>1.277199407923035e-05</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0002081318671116605</v>
+        <v>0.0001248142361873761</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0001213904688484035</v>
+        <v>3.813785951933824e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0002490545448381454</v>
+        <v>2.149943611584604e-06</v>
       </c>
       <c r="DD12" t="n">
-        <v>7.296265539480373e-05</v>
+        <v>3.224421743652783e-05</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0001614993234397843</v>
+        <v>0.0001529669971205294</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.0006422728765755892</v>
+        <v>0.000221498281462118</v>
       </c>
       <c r="DG12" t="n">
-        <v>8.139146666508168e-05</v>
+        <v>8.734423317946494e-05</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0006661233492195606</v>
+        <v>0.0002104080776916817</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0001930458092829213</v>
+        <v>0.0004888989496976137</v>
       </c>
       <c r="DJ12" t="n">
-        <v>6.080686580389738e-05</v>
+        <v>2.536958709242754e-05</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.00048056710511446</v>
+        <v>0.0001335291162831709</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0002608041977509856</v>
+        <v>2.088942346745171e-05</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0001872861466836184</v>
+        <v>2.012790355365723e-05</v>
       </c>
       <c r="DN12" t="n">
-        <v>5.242083716439083e-05</v>
+        <v>3.41979757649824e-05</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0002397190255578607</v>
+        <v>0.000284834677586332</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.0001710733631625772</v>
+        <v>2.730490450630896e-06</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0001152949262177572</v>
+        <v>0.0002309034898644313</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.31072757137008e-05</v>
+        <v>0.0002305788802914321</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0001442677166778594</v>
+        <v>1.48488561535487e-05</v>
       </c>
       <c r="DT12" t="n">
-        <v>3.871636727126315e-05</v>
+        <v>6.364214641507715e-05</v>
       </c>
       <c r="DU12" t="n">
-        <v>3.149677650071681e-05</v>
+        <v>0.0002515084925107658</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0001397049782099202</v>
+        <v>3.756284422706813e-05</v>
       </c>
       <c r="DW12" t="n">
-        <v>9.197938197758049e-06</v>
+        <v>0.0002149660867871717</v>
       </c>
       <c r="DX12" t="n">
-        <v>9.164528455585241e-05</v>
+        <v>6.602203939110041e-05</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.0002604040782898664</v>
+        <v>0.0001867039973149076</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0001332362007815391</v>
+        <v>2.370313268329483e-05</v>
       </c>
       <c r="EA12" t="n">
-        <v>8.582619193475693e-05</v>
+        <v>0.0002235266583738849</v>
       </c>
       <c r="EB12" t="n">
-        <v>9.367500751977786e-06</v>
+        <v>0.0001688911870587617</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.0001107246789615601</v>
+        <v>6.156302697490901e-05</v>
       </c>
       <c r="ED12" t="n">
-        <v>6.335033685900271e-05</v>
+        <v>4.317540879128501e-05</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0001111978635890409</v>
+        <v>0.0001721288281260058</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0001781302125891671</v>
+        <v>7.509297574870288e-05</v>
       </c>
       <c r="EG12" t="n">
-        <v>7.546191045548767e-05</v>
+        <v>0.0001320619776379317</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.0001260415592696518</v>
+        <v>8.072804121184163e-06</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0001599820971023291</v>
+        <v>5.882444384042174e-05</v>
       </c>
       <c r="EJ12" t="n">
-        <v>3.891254891641438e-05</v>
+        <v>7.176960207289085e-05</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0001603738055564463</v>
+        <v>7.641358388355002e-05</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.000129847670905292</v>
+        <v>8.346246613655239e-05</v>
       </c>
       <c r="EM12" t="n">
-        <v>1.937150955200195e-06</v>
+        <v>6.486861093435436e-05</v>
       </c>
       <c r="EN12" t="n">
-        <v>4.637120946426876e-05</v>
+        <v>1.30819680634886e-05</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.000121920027595479</v>
+        <v>7.135296618798748e-05</v>
       </c>
       <c r="EP12" t="n">
-        <v>7.020949851721525e-05</v>
+        <v>6.351497722789645e-05</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.000233657076023519</v>
+        <v>4.987553984392434e-05</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0001570386521052569</v>
+        <v>0.0001309521176153794</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0002211281680501997</v>
+        <v>0.0001996987411985174</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.000124470388982445</v>
+        <v>8.850946323946118e-05</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0001811746333260089</v>
+        <v>0.0001293595269089565</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.0003433638485148549</v>
+        <v>0.0001460884377593175</v>
       </c>
       <c r="EW12" t="n">
-        <v>1.054843960446306e-05</v>
+        <v>0.0001979584340006113</v>
       </c>
       <c r="EX12" t="n">
-        <v>1.936234548338689e-05</v>
+        <v>0.0001293625100515783</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.000257479608990252</v>
+        <v>0.0003424766182433814</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.0001473383890697733</v>
+        <v>5.899348252569325e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0002105490129906684</v>
+        <v>5.858693111804314e-05</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0001647733442950994</v>
+        <v>3.902675962308422e-05</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0001989010779652745</v>
+        <v>9.191132267005742e-05</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0001527340500615537</v>
+        <v>9.843899169936776e-05</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0001237339747603983</v>
+        <v>4.757839633384719e-05</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0001388162199873477</v>
+        <v>4.837222149944864e-05</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.0001264467864530161</v>
+        <v>3.425700197112747e-05</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0001456134195905179</v>
+        <v>0.0003226882836315781</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.0002637156285345554</v>
+        <v>7.655718945898116e-05</v>
       </c>
       <c r="FJ12" t="n">
-        <v>9.338092058897018e-05</v>
+        <v>0.0002462805714458227</v>
       </c>
       <c r="FK12" t="n">
-        <v>3.978882523369975e-05</v>
+        <v>0.0001709095085971057</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0001727837516227737</v>
+        <v>7.028505206108093e-05</v>
       </c>
       <c r="FM12" t="n">
-        <v>4.905177047476172e-05</v>
+        <v>0.0002215091517427936</v>
       </c>
       <c r="FN12" t="n">
-        <v>5.411005986388773e-05</v>
+        <v>0.0001681594003457576</v>
       </c>
       <c r="FO12" t="n">
-        <v>4.980673838872463e-05</v>
+        <v>0.0001278227427974343</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0001819244644138962</v>
+        <v>5.219883314566687e-05</v>
       </c>
       <c r="FQ12" t="n">
-        <v>7.826498767826706e-05</v>
+        <v>0.0001220201447722502</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.000100509831099771</v>
+        <v>1.491693546995521e-05</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0003990030381828547</v>
+        <v>0.0002708956017158926</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.0005222269683144987</v>
+        <v>0.0001553192705614492</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0002698902389965951</v>
+        <v>5.279311153572053e-06</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.0001626145240152255</v>
+        <v>2.588108873169404e-05</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0003525284118950367</v>
+        <v>0.0001412377750966698</v>
       </c>
       <c r="FX12" t="n">
-        <v>4.51361047453247e-05</v>
+        <v>0.0002278622414451092</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0002947589964605868</v>
+        <v>0.0002919293474406004</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.0001433214783901349</v>
+        <v>0.0001626067387405783</v>
       </c>
       <c r="GA12" t="n">
-        <v>7.672961510252208e-05</v>
+        <v>2.390563167864457e-05</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.0001989066076930612</v>
+        <v>0.0001125900744227692</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.0001160076790256426</v>
+        <v>4.380771133583039e-05</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0001216204909724183</v>
+        <v>8.440144301857799e-05</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.0007198548410087824</v>
+        <v>8.508373139193282e-05</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.0002765870885923505</v>
+        <v>0.0002160279836971313</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.000253595324466005</v>
+        <v>0.0001828598906286061</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.003381856251507998</v>
+        <v>0.03645642474293709</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02750666625797749</v>
+        <v>0.1936383098363876</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00345922727137804</v>
+        <v>0.01121208444237709</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01585974358022213</v>
+        <v>0.1485983580350876</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008561629801988602</v>
+        <v>0.02211380377411842</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006797817535698414</v>
+        <v>0.06286934018135071</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003316684160381556</v>
+        <v>0.04845606535673141</v>
       </c>
       <c r="H13" t="n">
-        <v>0.002199148992076516</v>
+        <v>0.06827697157859802</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0006387565517798066</v>
+        <v>0.009716736152768135</v>
       </c>
       <c r="J13" t="n">
-        <v>0.003029264742508531</v>
+        <v>0.006903971079736948</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02109759487211704</v>
+        <v>0.1957041025161743</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001262762234546244</v>
+        <v>0.003995049744844437</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01163801085203886</v>
+        <v>0.2213586717844009</v>
       </c>
       <c r="N13" t="n">
-        <v>0.007612952031195164</v>
+        <v>0.07415963709354401</v>
       </c>
       <c r="O13" t="n">
-        <v>0.008880028501152992</v>
+        <v>0.07456423342227936</v>
       </c>
       <c r="P13" t="n">
-        <v>0.002986926585435867</v>
+        <v>0.03338074311614037</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.005032915156334639</v>
+        <v>0.00549429003149271</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0007350823143497109</v>
+        <v>0.01899945735931396</v>
       </c>
       <c r="S13" t="n">
-        <v>0.002368038985878229</v>
+        <v>0.006729127839207649</v>
       </c>
       <c r="T13" t="n">
-        <v>0.004735673777759075</v>
+        <v>0.01723182387650013</v>
       </c>
       <c r="U13" t="n">
-        <v>0.001089980127289891</v>
+        <v>0.004914161749184132</v>
       </c>
       <c r="V13" t="n">
-        <v>0.004215527791529894</v>
+        <v>0.04110080003738403</v>
       </c>
       <c r="W13" t="n">
-        <v>0.001766532543115318</v>
+        <v>0.03672021627426147</v>
       </c>
       <c r="X13" t="n">
-        <v>0.003083971329033375</v>
+        <v>0.03227616846561432</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.003683035727590322</v>
+        <v>0.02303377166390419</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.003615392372012138</v>
+        <v>0.02542386762797832</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.003424052149057388</v>
+        <v>0.01114174444228411</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0006490671075880527</v>
+        <v>0.01548050064593554</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.047236557700671e-05</v>
+        <v>0.008118223398923874</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.001577868359163404</v>
+        <v>0.00666363537311554</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0007013370050117373</v>
+        <v>0.04000775888562202</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0005711046978831291</v>
+        <v>0.04259111359715462</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.001145146670751274</v>
+        <v>0.047133419662714</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.001988940173760056</v>
+        <v>0.007523373700678349</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.001810665591619909</v>
+        <v>0.05775702744722366</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.001482889172621071</v>
+        <v>0.02755319327116013</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.003266858402639627</v>
+        <v>0.002083567436784506</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.002741514006629586</v>
+        <v>0.04724344238638878</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0005948280449956656</v>
+        <v>0.02163404226303101</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.001861662487499416</v>
+        <v>0.04234541207551956</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.001940605347044766</v>
+        <v>0.009263725951313972</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.002466583624482155</v>
+        <v>0.02747533470392227</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.002091244328767061</v>
+        <v>0.0004756208509206772</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.002152922563254833</v>
+        <v>0.01866123080253601</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.002167148748412728</v>
+        <v>0.01081855408847332</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0005941829876974225</v>
+        <v>0.02916238829493523</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0180544052273035</v>
+        <v>0.1482167541980743</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.000767752411775291</v>
+        <v>0.03293243423104286</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0008820135262794793</v>
+        <v>0.05230432748794556</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0006677818601019681</v>
+        <v>0.1176434382796288</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0001862243079813197</v>
+        <v>0.05054948106408119</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.001501377322711051</v>
+        <v>0.006079120095819235</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.005018898285925388</v>
+        <v>0.02643395587801933</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.001515946700237691</v>
+        <v>0.01049879379570484</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.003386492375284433</v>
+        <v>0.01909999176859856</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.00392649881541729</v>
+        <v>0.02286515757441521</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.006057657767087221</v>
+        <v>0.01077165268361568</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.004725749604403973</v>
+        <v>0.03421759605407715</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.009371025487780571</v>
+        <v>0.04262463748455048</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.003214873373508453</v>
+        <v>0.01497668400406837</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0004881606146227568</v>
+        <v>0.001001324504613876</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.004937845747917891</v>
+        <v>0.06016471982002258</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0002784017706289887</v>
+        <v>0.02681396529078484</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.004167200997471809</v>
+        <v>0.001586164464242756</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.00519237807020545</v>
+        <v>0.01631239242851734</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.001989883603528142</v>
+        <v>0.01187271438539028</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.992066194768995e-05</v>
+        <v>0.009867332875728607</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.002314402721822262</v>
+        <v>0.02242691442370415</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.002695755567401648</v>
+        <v>0.01339736394584179</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0001942601957125589</v>
+        <v>0.04173293709754944</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.001815476571209729</v>
+        <v>0.009545939043164253</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0001037991314660758</v>
+        <v>0.01803782768547535</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0004269818018656224</v>
+        <v>0.001148916780948639</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.01031132694333792</v>
+        <v>0.08799434453248978</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.003785081207752228</v>
+        <v>0.01472904160618782</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.001436666701920331</v>
+        <v>0.06936255097389221</v>
       </c>
       <c r="BY13" t="n">
-        <v>4.26997066824697e-05</v>
+        <v>0.0256001204252243</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.003449102863669395</v>
+        <v>0.04510154575109482</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.003835452254861593</v>
+        <v>0.0287547055631876</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0004929412389174104</v>
+        <v>0.001382289920002222</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.001814763061702251</v>
+        <v>0.01424175687134266</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0002805478579830378</v>
+        <v>0.002063776133581996</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.004296991508454084</v>
+        <v>0.05929563194513321</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.001900401432067156</v>
+        <v>0.003575599519535899</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.001838797470554709</v>
+        <v>0.04686795920133591</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0008547063334845006</v>
+        <v>0.01107873767614365</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.002053645206615329</v>
+        <v>0.006056003738194704</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0009566076914779842</v>
+        <v>0.003379902336746454</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0009191387216560543</v>
+        <v>0.01641461439430714</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.002299633575603366</v>
+        <v>0.004383514635264874</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.002650545910000801</v>
+        <v>0.04406685009598732</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.001097809057682753</v>
+        <v>0.07044986635446548</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.00211274903267622</v>
+        <v>0.06942947208881378</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.00490501569584012</v>
+        <v>0.1109946817159653</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.003886985126882792</v>
+        <v>0.009464770555496216</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.003393219318240881</v>
+        <v>0.023298604413867</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.004580348264425993</v>
+        <v>0.02715751528739929</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.002843455411493778</v>
+        <v>0.02261823229491711</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.001080685527995229</v>
+        <v>0.01122711226344109</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0004030192212667316</v>
+        <v>0.005000650882720947</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.003606016980484128</v>
+        <v>0.05442104488611221</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.001760873943567276</v>
+        <v>0.002395331393927336</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.002916409634053707</v>
+        <v>0.05304989218711853</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.001017317292280495</v>
+        <v>0.0148770734667778</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.002449001185595989</v>
+        <v>0.008716519922018051</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.001429633121006191</v>
+        <v>0.001916347770020366</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.001438913750462234</v>
+        <v>0.01753351092338562</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.001499258796684444</v>
+        <v>0.00463849538937211</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0004529225407168269</v>
+        <v>0.01591464504599571</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.005281864665448666</v>
+        <v>0.01663929224014282</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.006632262840867043</v>
+        <v>0.006503540091216564</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.01291297655552626</v>
+        <v>0.0502689927816391</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001406370894983411</v>
+        <v>0.04152208939194679</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.002259049331769347</v>
+        <v>0.01995179429650307</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.001093168742954731</v>
+        <v>0.0007809256203472614</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.001283623510971665</v>
+        <v>0.07869799435138702</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.001540339435450733</v>
+        <v>0.01810359209775925</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.00265469285659492</v>
+        <v>0.01162212342023849</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.002295565791428089</v>
+        <v>0.03438994288444519</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0003079090965911746</v>
+        <v>0.00385716650635004</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0009882927406579256</v>
+        <v>0.011747513897717</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.001702368608675897</v>
+        <v>0.008874774910509586</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.001397596439346671</v>
+        <v>0.006725241895765066</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.002004986628890038</v>
+        <v>0.02801553159952164</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.001017066184431314</v>
+        <v>0.03079651668667793</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.003905379679054022</v>
+        <v>0.01876487582921982</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.001894872635602951</v>
+        <v>0.02732257731258869</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0004764184704981744</v>
+        <v>0.0122295031324029</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.004247114062309265</v>
+        <v>0.03846100345253944</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0004426373343449086</v>
+        <v>0.03428937494754791</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.001983868423849344</v>
+        <v>0.00888835359364748</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.002341662533581257</v>
+        <v>0.01148942951112986</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0002362483210163191</v>
+        <v>0.01453052461147308</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0004716120311059058</v>
+        <v>0.06963236629962921</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.002820783527567983</v>
+        <v>0.04170363396406174</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.002615269040688872</v>
+        <v>0.02490954287350178</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.004231125116348267</v>
+        <v>0.01784553378820419</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.001029687118716538</v>
+        <v>0.02127895876765251</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.001031880150549114</v>
+        <v>0.03323915600776672</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.002070056973025203</v>
+        <v>0.0127274664118886</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.001995876198634505</v>
+        <v>0.001685013179667294</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.001869191648438573</v>
+        <v>0.001516594085842371</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0003835872339550406</v>
+        <v>0.01024489663541317</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.001047655241563916</v>
+        <v>0.00327404448762536</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0002295633894391358</v>
+        <v>0.01612693071365356</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0008062532288022339</v>
+        <v>0.04555652290582657</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.003176656784489751</v>
+        <v>0.0106758251786232</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.001185197848826647</v>
+        <v>0.03184409812092781</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0003976101870648563</v>
+        <v>0.01347226276993752</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.002943801693618298</v>
+        <v>0.005893955938518047</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.002402843441814184</v>
+        <v>0.01802041754126549</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.002895059529691935</v>
+        <v>0.01243255380541086</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.001747118076309562</v>
+        <v>0.01996251009404659</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0001393561105942354</v>
+        <v>0.003962226212024689</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.003575462847948074</v>
+        <v>0.06154188141226768</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.00153956119902432</v>
+        <v>0.002771956846117973</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.002375703537836671</v>
+        <v>0.06094416603446007</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0005070041515864432</v>
+        <v>0.005365341901779175</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.002206528326496482</v>
+        <v>0.0072572804056108</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.001699160202406347</v>
+        <v>0.009702088311314583</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0008221002062782645</v>
+        <v>0.02233576402068138</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.002342301420867443</v>
+        <v>0.002370525151491165</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.002573002595454454</v>
+        <v>0.004433612339198589</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.001873187604360282</v>
+        <v>0.03213183209300041</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.003068911377340555</v>
+        <v>0.01016828417778015</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.003053660737350583</v>
+        <v>0.03963742777705193</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.002204987453296781</v>
+        <v>0.004934948403388262</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.001658075489103794</v>
+        <v>0.0115312309935689</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.002213317900896072</v>
+        <v>0.02320420742034912</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.002271126490086317</v>
+        <v>0.008300184272229671</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0001919780188472942</v>
+        <v>0.02505712583661079</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.001245969324372709</v>
+        <v>0.03602500259876251</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0006428735796362162</v>
+        <v>0.07043729722499847</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.003713092766702175</v>
+        <v>0.03021344728767872</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0006662847008556128</v>
+        <v>0.050637137144804</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.002462059492245317</v>
+        <v>0.005878356285393238</v>
       </c>
       <c r="FU13" t="n">
-        <v>3.435142571106553e-05</v>
+        <v>0.009990477003157139</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0008334602462127805</v>
+        <v>0.01863722875714302</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0001282221346627921</v>
+        <v>0.03460994362831116</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.002384300343692303</v>
+        <v>0.009569127112627029</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.004196219146251678</v>
+        <v>0.01951681450009346</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.002038245089352131</v>
+        <v>0.0156091321259737</v>
       </c>
       <c r="GA13" t="n">
-        <v>8.879058441380039e-05</v>
+        <v>0.03589227423071861</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0005974278901703656</v>
+        <v>0.04981660842895508</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.003585017286241055</v>
+        <v>0.003079080022871494</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.003601827193051577</v>
+        <v>0.02451039105653763</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.007456663064658642</v>
+        <v>0.05909404531121254</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.003316719783470035</v>
+        <v>0.02077548392117023</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.004019996151328087</v>
+        <v>0.0037067043595016</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1.713806796033168e-06</v>
+        <v>0.0144870076328516</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0001589349849382415</v>
+        <v>0.0260375589132309</v>
       </c>
       <c r="C14" t="n">
-        <v>3.219598511350341e-06</v>
+        <v>0.01190829556435347</v>
       </c>
       <c r="D14" t="n">
-        <v>4.068197085871361e-05</v>
+        <v>0.0115196704864502</v>
       </c>
       <c r="E14" t="n">
-        <v>5.513967698789202e-05</v>
+        <v>0.02921240776777267</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0002186748461099342</v>
+        <v>0.06254962086677551</v>
       </c>
       <c r="G14" t="n">
-        <v>1.918842099257745e-05</v>
+        <v>0.008628223091363907</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0001093304017558694</v>
+        <v>0.04590350762009621</v>
       </c>
       <c r="I14" t="n">
-        <v>2.498055619071238e-05</v>
+        <v>0.01266404427587986</v>
       </c>
       <c r="J14" t="n">
-        <v>2.532666439947207e-05</v>
+        <v>0.007715065497905016</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0001285065955016762</v>
+        <v>0.0395142063498497</v>
       </c>
       <c r="L14" t="n">
-        <v>3.363811629242264e-05</v>
+        <v>0.0116122905164957</v>
       </c>
       <c r="M14" t="n">
-        <v>1.604647150088567e-05</v>
+        <v>0.006439715623855591</v>
       </c>
       <c r="N14" t="n">
-        <v>2.723426587181166e-05</v>
+        <v>0.04839633777737617</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0001938197819981724</v>
+        <v>0.07229145616292953</v>
       </c>
       <c r="P14" t="n">
-        <v>2.176566340494901e-06</v>
+        <v>0.002785704331472516</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.528582839062437e-05</v>
+        <v>0.03360873833298683</v>
       </c>
       <c r="R14" t="n">
-        <v>3.619282779254718e-06</v>
+        <v>0.01886134035885334</v>
       </c>
       <c r="S14" t="n">
-        <v>2.552919795562048e-07</v>
+        <v>0.006795482710003853</v>
       </c>
       <c r="T14" t="n">
-        <v>1.870217602117918e-06</v>
+        <v>0.01674520783126354</v>
       </c>
       <c r="U14" t="n">
-        <v>2.31074864132097e-07</v>
+        <v>0.005778739228844643</v>
       </c>
       <c r="V14" t="n">
-        <v>2.7747430067393e-05</v>
+        <v>0.02124243788421154</v>
       </c>
       <c r="W14" t="n">
-        <v>5.326824248186313e-05</v>
+        <v>0.01627120561897755</v>
       </c>
       <c r="X14" t="n">
-        <v>2.768543163256254e-05</v>
+        <v>0.01212239637970924</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.655694051005412e-06</v>
+        <v>0.005398320499807596</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.063950276147807e-05</v>
+        <v>0.009979767724871635</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.090684903232614e-06</v>
+        <v>0.00356354215182364</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.26613929044106e-06</v>
+        <v>0.0005881040124222636</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.812279126374051e-05</v>
+        <v>0.01500304229557514</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.026861329795793e-05</v>
+        <v>0.004468701779842377</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.744439941830933e-06</v>
+        <v>0.02246873825788498</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.904234522953629e-06</v>
+        <v>0.02414947934448719</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.259936470887624e-05</v>
+        <v>0.01204907335340977</v>
       </c>
       <c r="AH14" t="n">
-        <v>5.139831500855507e-06</v>
+        <v>0.006600206717848778</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.176283512904774e-05</v>
+        <v>0.03059725649654865</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.499558402429102e-05</v>
+        <v>0.008840837515890598</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.861624696175568e-05</v>
+        <v>0.003676246386021376</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.68922033481067e-05</v>
+        <v>0.02764031104743481</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.667564720264636e-05</v>
+        <v>0.0008942959830164909</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.456867721572053e-05</v>
+        <v>0.004734957590699196</v>
       </c>
       <c r="AO14" t="n">
-        <v>1.906941861307132e-06</v>
+        <v>0.01321954838931561</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.208183286711574e-05</v>
+        <v>0.01713956892490387</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.295932517881738e-06</v>
+        <v>0.009554974734783173</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.330597751802998e-05</v>
+        <v>0.01539911702275276</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.62396247308061e-06</v>
+        <v>0.005437682382762432</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.6876137831714e-06</v>
+        <v>0.003201460465788841</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.357882325071841e-05</v>
+        <v>0.1104255318641663</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.596697231638245e-05</v>
+        <v>0.006897538434714079</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.604988862411119e-05</v>
+        <v>0.002467792015522718</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.967415588907897e-05</v>
+        <v>0.001873489236459136</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0001180670806206763</v>
+        <v>0.05099283903837204</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.607932219689246e-05</v>
+        <v>0.001529577188193798</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.420098124071956e-05</v>
+        <v>0.008237112313508987</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.697802872513421e-05</v>
+        <v>0.004797214642167091</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.688934025878552e-05</v>
+        <v>0.01074624992907047</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.529607031145133e-05</v>
+        <v>0.03887301683425903</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.760752249741927e-05</v>
+        <v>5.369330756366253e-05</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.619143222342245e-05</v>
+        <v>0.0002687834203243256</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.931056769739371e-05</v>
+        <v>0.03077959269285202</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.447094033821486e-05</v>
+        <v>0.000574896577745676</v>
       </c>
       <c r="BI14" t="n">
-        <v>4.097943474334897e-06</v>
+        <v>0.01018303353339434</v>
       </c>
       <c r="BJ14" t="n">
-        <v>3.390906204003841e-05</v>
+        <v>0.0130024328827858</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.963065369636752e-05</v>
+        <v>0.0002857710933312774</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.302643977396656e-05</v>
+        <v>0.008134931325912476</v>
       </c>
       <c r="BM14" t="n">
-        <v>4.175494541414082e-05</v>
+        <v>0.01886808685958385</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.610254159662873e-05</v>
+        <v>0.01816598698496819</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.782217077561654e-05</v>
+        <v>0.0001364070922136307</v>
       </c>
       <c r="BP14" t="n">
-        <v>1.267875177290989e-05</v>
+        <v>0.02013395167887211</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.809806680190377e-06</v>
+        <v>0.005444875452667475</v>
       </c>
       <c r="BR14" t="n">
-        <v>1.612181222299114e-06</v>
+        <v>0.02729030139744282</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.579959098307882e-05</v>
+        <v>0.00492317508906126</v>
       </c>
       <c r="BT14" t="n">
-        <v>6.029045835020952e-06</v>
+        <v>0.01138441544026136</v>
       </c>
       <c r="BU14" t="n">
-        <v>5.971492100798059e-06</v>
+        <v>0.001930900383740664</v>
       </c>
       <c r="BV14" t="n">
-        <v>5.935759691055864e-05</v>
+        <v>0.0493057519197464</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.330882802605629e-06</v>
+        <v>0.003545719664543867</v>
       </c>
       <c r="BX14" t="n">
-        <v>1.985926974157337e-05</v>
+        <v>0.006671757437288761</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.748122485878412e-05</v>
+        <v>0.01404049247503281</v>
       </c>
       <c r="BZ14" t="n">
-        <v>7.717970584053546e-05</v>
+        <v>0.03592149540781975</v>
       </c>
       <c r="CA14" t="n">
-        <v>8.356460057257209e-07</v>
+        <v>0.01157319266349077</v>
       </c>
       <c r="CB14" t="n">
-        <v>5.316525857779197e-06</v>
+        <v>0.009195380844175816</v>
       </c>
       <c r="CC14" t="n">
-        <v>8.07254127721535e-06</v>
+        <v>0.0006370595074258745</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.969001681980444e-06</v>
+        <v>0.001832384616136551</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.96447545022238e-05</v>
+        <v>0.0142065342515707</v>
       </c>
       <c r="CF14" t="n">
-        <v>4.558013642963488e-06</v>
+        <v>0.007208318915218115</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.252274953207234e-07</v>
+        <v>0.004024895373731852</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.758895632519852e-05</v>
+        <v>0.01054919138550758</v>
       </c>
       <c r="CI14" t="n">
-        <v>4.140562668908387e-05</v>
+        <v>0.01748842932283878</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.148338196799159e-05</v>
+        <v>0.01019492372870445</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.735335899866186e-05</v>
+        <v>0.003758618608117104</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.480741613908322e-06</v>
+        <v>0.00344177708029747</v>
       </c>
       <c r="CM14" t="n">
-        <v>1.61543684953358e-05</v>
+        <v>0.01654243096709251</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.248784974450245e-05</v>
+        <v>0.04646181687712669</v>
       </c>
       <c r="CO14" t="n">
-        <v>5.155265171197243e-06</v>
+        <v>0.004408527165651321</v>
       </c>
       <c r="CP14" t="n">
-        <v>8.833314495859668e-06</v>
+        <v>0.01045547146350145</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.328585444251075e-05</v>
+        <v>0.02282771840691566</v>
       </c>
       <c r="CR14" t="n">
-        <v>3.191297309967922e-06</v>
+        <v>0.0199317242950201</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.488804602762684e-05</v>
+        <v>0.002436291426420212</v>
       </c>
       <c r="CT14" t="n">
-        <v>1.96207929548109e-05</v>
+        <v>0.01193324849009514</v>
       </c>
       <c r="CU14" t="n">
-        <v>2.843161928467453e-05</v>
+        <v>0.003990254364907742</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.296239472343586e-06</v>
+        <v>0.005500032566487789</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.509287812950788e-05</v>
+        <v>0.00934819970279932</v>
       </c>
       <c r="CX14" t="n">
-        <v>5.694796527677681e-06</v>
+        <v>0.007621395401656628</v>
       </c>
       <c r="CY14" t="n">
-        <v>5.207401045481674e-06</v>
+        <v>0.0002661721082404256</v>
       </c>
       <c r="CZ14" t="n">
-        <v>9.19586636882741e-06</v>
+        <v>0.0104272672906518</v>
       </c>
       <c r="DA14" t="n">
-        <v>3.850407301797532e-05</v>
+        <v>0.01880834996700287</v>
       </c>
       <c r="DB14" t="n">
-        <v>8.442193575319834e-06</v>
+        <v>0.004072059411555529</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.218375084339641e-05</v>
+        <v>0.004463077057152987</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.275159775104839e-05</v>
+        <v>0.003563799662515521</v>
       </c>
       <c r="DE14" t="n">
-        <v>3.130217010038905e-05</v>
+        <v>0.0121453395113349</v>
       </c>
       <c r="DF14" t="n">
-        <v>4.494071617955342e-06</v>
+        <v>0.002127915620803833</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.638532467040932e-06</v>
+        <v>0.009559012949466705</v>
       </c>
       <c r="DH14" t="n">
-        <v>8.243185584433377e-05</v>
+        <v>0.005557633005082607</v>
       </c>
       <c r="DI14" t="n">
-        <v>4.23089149990119e-05</v>
+        <v>0.006477095652371645</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.58976906479802e-05</v>
+        <v>0.002554061124101281</v>
       </c>
       <c r="DK14" t="n">
-        <v>8.270121725217905e-07</v>
+        <v>0.01364468038082123</v>
       </c>
       <c r="DL14" t="n">
-        <v>3.259180812165141e-05</v>
+        <v>0.01302322838455439</v>
       </c>
       <c r="DM14" t="n">
-        <v>3.191432915627956e-05</v>
+        <v>0.01332470960915089</v>
       </c>
       <c r="DN14" t="n">
-        <v>5.107410288474057e-06</v>
+        <v>0.001986741553992033</v>
       </c>
       <c r="DO14" t="n">
-        <v>7.099426511558704e-06</v>
+        <v>0.006411787588149309</v>
       </c>
       <c r="DP14" t="n">
-        <v>2.541526191635057e-05</v>
+        <v>0.005797017365694046</v>
       </c>
       <c r="DQ14" t="n">
-        <v>8.719256584299728e-06</v>
+        <v>0.02272121608257294</v>
       </c>
       <c r="DR14" t="n">
-        <v>2.193074942624662e-05</v>
+        <v>0.00222685863263905</v>
       </c>
       <c r="DS14" t="n">
-        <v>3.494685006444342e-05</v>
+        <v>0.01089711487293243</v>
       </c>
       <c r="DT14" t="n">
-        <v>1.556160168547649e-05</v>
+        <v>0.001501138904131949</v>
       </c>
       <c r="DU14" t="n">
-        <v>1.411533958162181e-05</v>
+        <v>0.007920399308204651</v>
       </c>
       <c r="DV14" t="n">
-        <v>1.419978161720792e-05</v>
+        <v>0.009186964482069016</v>
       </c>
       <c r="DW14" t="n">
-        <v>7.803302651154809e-06</v>
+        <v>0.002683778060600162</v>
       </c>
       <c r="DX14" t="n">
-        <v>3.527609351294814e-06</v>
+        <v>0.02031603828072548</v>
       </c>
       <c r="DY14" t="n">
-        <v>3.658328751043882e-06</v>
+        <v>0.01167929265648127</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1.595640969753731e-05</v>
+        <v>0.00383608927950263</v>
       </c>
       <c r="EA14" t="n">
-        <v>9.675518413132522e-06</v>
+        <v>0.01362211350351572</v>
       </c>
       <c r="EB14" t="n">
-        <v>2.69149495579768e-05</v>
+        <v>0.01128249615430832</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.04201342057786e-06</v>
+        <v>0.001182593638077378</v>
       </c>
       <c r="ED14" t="n">
-        <v>7.868554348533507e-06</v>
+        <v>0.006842439062893391</v>
       </c>
       <c r="EE14" t="n">
-        <v>2.225013668066822e-05</v>
+        <v>0.0007318708230741322</v>
       </c>
       <c r="EF14" t="n">
-        <v>2.906750523834489e-06</v>
+        <v>0.006353386677801609</v>
       </c>
       <c r="EG14" t="n">
-        <v>1.40266402013367e-05</v>
+        <v>0.007126952521502972</v>
       </c>
       <c r="EH14" t="n">
-        <v>7.844289029890206e-06</v>
+        <v>0.00624464126303792</v>
       </c>
       <c r="EI14" t="n">
-        <v>2.422758007014636e-05</v>
+        <v>0.00820615328848362</v>
       </c>
       <c r="EJ14" t="n">
-        <v>1.019486353470711e-05</v>
+        <v>0.003544581588357687</v>
       </c>
       <c r="EK14" t="n">
-        <v>1.67824218806345e-05</v>
+        <v>0.005352912005037069</v>
       </c>
       <c r="EL14" t="n">
-        <v>7.772740900691133e-06</v>
+        <v>0.002102947793900967</v>
       </c>
       <c r="EM14" t="n">
-        <v>9.531366231385618e-06</v>
+        <v>0.001795744174160063</v>
       </c>
       <c r="EN14" t="n">
-        <v>4.300372893339954e-06</v>
+        <v>0.004794764798134565</v>
       </c>
       <c r="EO14" t="n">
-        <v>1.367186882816895e-06</v>
+        <v>0.0003820387646555901</v>
       </c>
       <c r="EP14" t="n">
-        <v>7.432019629050046e-06</v>
+        <v>0.006938595324754715</v>
       </c>
       <c r="EQ14" t="n">
-        <v>1.57880913320696e-05</v>
+        <v>0.001677917316555977</v>
       </c>
       <c r="ER14" t="n">
-        <v>4.236111635691486e-06</v>
+        <v>0.003821091260761023</v>
       </c>
       <c r="ES14" t="n">
-        <v>5.832543138239998e-06</v>
+        <v>0.00428664917126298</v>
       </c>
       <c r="ET14" t="n">
-        <v>1.37404431370669e-05</v>
+        <v>0.01182093471288681</v>
       </c>
       <c r="EU14" t="n">
-        <v>1.100934696296463e-06</v>
+        <v>0.01090961042791605</v>
       </c>
       <c r="EV14" t="n">
-        <v>7.113902393030003e-05</v>
+        <v>0.003216296434402466</v>
       </c>
       <c r="EW14" t="n">
-        <v>2.096095704473555e-05</v>
+        <v>0.005165193229913712</v>
       </c>
       <c r="EX14" t="n">
-        <v>8.874568493411061e-07</v>
+        <v>0.003551687346771359</v>
       </c>
       <c r="EY14" t="n">
-        <v>1.344917382084532e-05</v>
+        <v>0.01465858891606331</v>
       </c>
       <c r="EZ14" t="n">
-        <v>1.448357579647563e-06</v>
+        <v>0.007366805337369442</v>
       </c>
       <c r="FA14" t="n">
-        <v>5.486833742907038e-07</v>
+        <v>0.001625669887289405</v>
       </c>
       <c r="FB14" t="n">
-        <v>1.892425098048989e-05</v>
+        <v>0.008041185326874256</v>
       </c>
       <c r="FC14" t="n">
-        <v>3.898625436704606e-05</v>
+        <v>0.01807983033359051</v>
       </c>
       <c r="FD14" t="n">
-        <v>1.321368745266227e-05</v>
+        <v>0.009458526968955994</v>
       </c>
       <c r="FE14" t="n">
-        <v>2.014843266806565e-05</v>
+        <v>0.003766318084672093</v>
       </c>
       <c r="FF14" t="n">
-        <v>7.312291472771903e-06</v>
+        <v>0.001631003804504871</v>
       </c>
       <c r="FG14" t="n">
-        <v>1.277522551390575e-05</v>
+        <v>0.01195047702640295</v>
       </c>
       <c r="FH14" t="n">
-        <v>2.075798147416208e-05</v>
+        <v>0.01517963781952858</v>
       </c>
       <c r="FI14" t="n">
-        <v>7.849121175240725e-06</v>
+        <v>0.006763063371181488</v>
       </c>
       <c r="FJ14" t="n">
-        <v>4.732578236144036e-05</v>
+        <v>0.02560399100184441</v>
       </c>
       <c r="FK14" t="n">
-        <v>6.037973435013555e-06</v>
+        <v>0.0008154942188411951</v>
       </c>
       <c r="FL14" t="n">
-        <v>8.653847544337623e-06</v>
+        <v>0.00940378662198782</v>
       </c>
       <c r="FM14" t="n">
-        <v>9.836670869844966e-06</v>
+        <v>0.009389147162437439</v>
       </c>
       <c r="FN14" t="n">
-        <v>5.484741450345609e-06</v>
+        <v>0.01408669166266918</v>
       </c>
       <c r="FO14" t="n">
-        <v>6.891988959978335e-06</v>
+        <v>0.006067227106541395</v>
       </c>
       <c r="FP14" t="n">
-        <v>4.443362195161171e-05</v>
+        <v>0.00590285612270236</v>
       </c>
       <c r="FQ14" t="n">
-        <v>1.851501474448014e-05</v>
+        <v>0.02754466608166695</v>
       </c>
       <c r="FR14" t="n">
-        <v>1.773328222043347e-06</v>
+        <v>0.01619941368699074</v>
       </c>
       <c r="FS14" t="n">
-        <v>5.270522706268821e-06</v>
+        <v>0.01780815422534943</v>
       </c>
       <c r="FT14" t="n">
-        <v>1.712070661596954e-05</v>
+        <v>0.01313443575054407</v>
       </c>
       <c r="FU14" t="n">
-        <v>3.123701753793284e-05</v>
+        <v>0.01843498833477497</v>
       </c>
       <c r="FV14" t="n">
-        <v>2.138618947356008e-05</v>
+        <v>0.006673578172922134</v>
       </c>
       <c r="FW14" t="n">
-        <v>4.519661160884425e-05</v>
+        <v>0.006920884363353252</v>
       </c>
       <c r="FX14" t="n">
-        <v>3.135751103400253e-05</v>
+        <v>0.0154866948723793</v>
       </c>
       <c r="FY14" t="n">
-        <v>1.815892392187379e-05</v>
+        <v>0.0005794886965304613</v>
       </c>
       <c r="FZ14" t="n">
-        <v>3.012112529177102e-06</v>
+        <v>0.001094760838896036</v>
       </c>
       <c r="GA14" t="n">
-        <v>1.398491531290347e-05</v>
+        <v>0.0187949500977993</v>
       </c>
       <c r="GB14" t="n">
-        <v>9.002181286632549e-06</v>
+        <v>0.01355734094977379</v>
       </c>
       <c r="GC14" t="n">
-        <v>5.503243301063776e-05</v>
+        <v>0.01207923609763384</v>
       </c>
       <c r="GD14" t="n">
-        <v>2.142789526260458e-05</v>
+        <v>0.001710430951789021</v>
       </c>
       <c r="GE14" t="n">
-        <v>2.200248673034366e-05</v>
+        <v>0.007828063331544399</v>
       </c>
       <c r="GF14" t="n">
-        <v>1.213109953823732e-05</v>
+        <v>0.005875540897250175</v>
       </c>
       <c r="GG14" t="n">
-        <v>1.170076757261995e-05</v>
+        <v>0.002369738882407546</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.507291017333046e-05</v>
+        <v>0.0005871466710232198</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0001732681266730651</v>
+        <v>0.002574329497292638</v>
       </c>
       <c r="C15" t="n">
-        <v>4.092710241820896e-06</v>
+        <v>0.0004235212109051645</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0001146810027421452</v>
+        <v>0.0009381164563819766</v>
       </c>
       <c r="E15" t="n">
-        <v>2.574283462308813e-05</v>
+        <v>0.000719836913049221</v>
       </c>
       <c r="F15" t="n">
-        <v>3.524883140926249e-05</v>
+        <v>0.002331874798983335</v>
       </c>
       <c r="G15" t="n">
-        <v>2.386650339758489e-05</v>
+        <v>0.001261327299289405</v>
       </c>
       <c r="H15" t="n">
-        <v>3.314153218525462e-05</v>
+        <v>0.001445758389309049</v>
       </c>
       <c r="I15" t="n">
-        <v>4.305451966502005e-06</v>
+        <v>0.0006812731735408306</v>
       </c>
       <c r="J15" t="n">
-        <v>6.737584953953046e-06</v>
+        <v>0.0008510671323165298</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0001626966113690287</v>
+        <v>0.003213794436305761</v>
       </c>
       <c r="L15" t="n">
-        <v>1.049534785124706e-05</v>
+        <v>0.00106937694363296</v>
       </c>
       <c r="M15" t="n">
-        <v>9.735051571624354e-05</v>
+        <v>0.002011628123000264</v>
       </c>
       <c r="N15" t="n">
-        <v>3.474612458376214e-05</v>
+        <v>0.0001031132997013628</v>
       </c>
       <c r="O15" t="n">
-        <v>7.98085420683492e-06</v>
+        <v>0.002176596317440271</v>
       </c>
       <c r="P15" t="n">
-        <v>1.159262410510564e-05</v>
+        <v>0.0005603950121439993</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.783932748367079e-05</v>
+        <v>0.0002012316253967583</v>
       </c>
       <c r="R15" t="n">
-        <v>1.219555088027846e-05</v>
+        <v>0.001226244494318962</v>
       </c>
       <c r="S15" t="n">
-        <v>1.098648863262497e-05</v>
+        <v>5.087026875116862e-05</v>
       </c>
       <c r="T15" t="n">
-        <v>2.852688339771703e-05</v>
+        <v>0.0002305987436557189</v>
       </c>
       <c r="U15" t="n">
-        <v>4.46408648713259e-07</v>
+        <v>0.0005250755930319428</v>
       </c>
       <c r="V15" t="n">
-        <v>8.862688446242828e-06</v>
+        <v>0.0001040629867929965</v>
       </c>
       <c r="W15" t="n">
-        <v>4.452945631783223e-06</v>
+        <v>0.0003631989238783717</v>
       </c>
       <c r="X15" t="n">
-        <v>2.349145461266744e-06</v>
+        <v>0.0009028949425555766</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.552517824165989e-05</v>
+        <v>0.000416420487454161</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.782301271508913e-05</v>
+        <v>7.50715407775715e-05</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.896781006711535e-05</v>
+        <v>0.0001265037863049656</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.865817805286497e-07</v>
+        <v>0.0002419148950139061</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.718642255989835e-05</v>
+        <v>0.0001433507713954896</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.243574726890074e-06</v>
+        <v>3.476089477771893e-05</v>
       </c>
       <c r="AE15" t="n">
-        <v>4.272265869076364e-06</v>
+        <v>0.0009100913885049522</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.666644493525382e-05</v>
+        <v>0.0006475088302977383</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.444246026949259e-05</v>
+        <v>0.001183860469609499</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.635039916436654e-05</v>
+        <v>0.0003463518223725259</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.557692697446328e-06</v>
+        <v>0.001677875407040119</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.117835563491099e-05</v>
+        <v>0.0002938759280368686</v>
       </c>
       <c r="AK15" t="n">
-        <v>9.041566045198124e-06</v>
+        <v>0.0002023264387389645</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.242305163235869e-05</v>
+        <v>0.0005076339584775269</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.693227315830882e-06</v>
+        <v>0.0006060705054551363</v>
       </c>
       <c r="AN15" t="n">
-        <v>9.20095499168383e-06</v>
+        <v>0.0002618829312268645</v>
       </c>
       <c r="AO15" t="n">
-        <v>2.669798595889006e-05</v>
+        <v>0.0001292936794925481</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.419385534973117e-05</v>
+        <v>0.0006342605920508504</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.274605503771454e-05</v>
+        <v>0.0002295126614626497</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.077268098015338e-05</v>
+        <v>0.0008535174420103431</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.115846202992543e-06</v>
+        <v>6.976502481848001e-05</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.610560113680549e-05</v>
+        <v>0.0004624832654371858</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.0001255999086424708</v>
+        <v>0.002745947800576687</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.745951678662095e-05</v>
+        <v>0.0009862065780907869</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.770624607568607e-05</v>
+        <v>0.0009241537773050368</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.850115030625602e-06</v>
+        <v>0.001224173698574305</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.721517259691609e-06</v>
+        <v>0.001989711541682482</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.051415766705759e-06</v>
+        <v>0.000174141867319122</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.615922155906446e-05</v>
+        <v>1.890752173494548e-05</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.647276783653069e-06</v>
+        <v>0.0004107518470846117</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.012447996297851e-05</v>
+        <v>0.0003624444943852723</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.015504287555814e-05</v>
+        <v>0.0001101256930269301</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.439937790972181e-05</v>
+        <v>0.000326341949403286</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.689718364010332e-06</v>
+        <v>0.0002651871473062783</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.454604691592976e-05</v>
+        <v>0.0006091154646128416</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.434586349409074e-05</v>
+        <v>0.0007638849783688784</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.275898284802679e-06</v>
+        <v>0.0006836291286163032</v>
       </c>
       <c r="BJ15" t="n">
-        <v>3.231464506825432e-05</v>
+        <v>0.0007119099027477205</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.135072307079099e-05</v>
+        <v>0.0007864509825594723</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.526403866591863e-05</v>
+        <v>8.497524686390534e-05</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.039126047748141e-05</v>
+        <v>0.0008563428418710828</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.167889968201052e-05</v>
+        <v>0.0001268685155082494</v>
       </c>
       <c r="BO15" t="n">
-        <v>6.764459158148384e-06</v>
+        <v>0.0001194959040731192</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.519689198583364e-05</v>
+        <v>0.0006041304441168904</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.45550166052999e-05</v>
+        <v>0.000138727089506574</v>
       </c>
       <c r="BR15" t="n">
-        <v>9.332897207059432e-06</v>
+        <v>0.0008723504142835736</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.038270238495898e-05</v>
+        <v>6.457760173361748e-05</v>
       </c>
       <c r="BT15" t="n">
-        <v>1.820501529437024e-05</v>
+        <v>0.0005409673904068768</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.22930368888774e-05</v>
+        <v>3.693189137266017e-05</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.437956471927464e-05</v>
+        <v>0.001621622126549482</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.921134288655594e-06</v>
+        <v>0.0006717406213283539</v>
       </c>
       <c r="BX15" t="n">
-        <v>2.258395034004934e-05</v>
+        <v>0.001131510245613754</v>
       </c>
       <c r="BY15" t="n">
-        <v>7.764637302898336e-06</v>
+        <v>0.0003437740379013121</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.42771272698883e-06</v>
+        <v>0.0009078407310880721</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.764852095220704e-05</v>
+        <v>0.0004894461599178612</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.188563252682798e-06</v>
+        <v>0.0004549475852400064</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.149945430574007e-05</v>
+        <v>0.0001866235688794404</v>
       </c>
       <c r="CD15" t="n">
-        <v>9.261165132556926e-07</v>
+        <v>5.538245750358328e-05</v>
       </c>
       <c r="CE15" t="n">
-        <v>2.992691406689119e-05</v>
+        <v>0.0008750548586249352</v>
       </c>
       <c r="CF15" t="n">
-        <v>5.601228167506633e-06</v>
+        <v>0.000112629852083046</v>
       </c>
       <c r="CG15" t="n">
-        <v>8.558399713365361e-06</v>
+        <v>0.0003556792798917741</v>
       </c>
       <c r="CH15" t="n">
-        <v>7.006854957580799e-06</v>
+        <v>1.348380465060472e-07</v>
       </c>
       <c r="CI15" t="n">
-        <v>7.136993644962786e-06</v>
+        <v>0.0001135088605224155</v>
       </c>
       <c r="CJ15" t="n">
-        <v>3.848591404675972e-06</v>
+        <v>0.0001152454642578959</v>
       </c>
       <c r="CK15" t="n">
-        <v>3.643313675638638e-06</v>
+        <v>0.0005572474328801036</v>
       </c>
       <c r="CL15" t="n">
-        <v>6.293703791016014e-06</v>
+        <v>0.0001439483748981729</v>
       </c>
       <c r="CM15" t="n">
-        <v>5.444662383524701e-05</v>
+        <v>0.0001539865334052593</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.70930888998555e-05</v>
+        <v>0.001021141768433154</v>
       </c>
       <c r="CO15" t="n">
-        <v>3.078973804804264e-06</v>
+        <v>0.001300007454119623</v>
       </c>
       <c r="CP15" t="n">
-        <v>4.677734614233486e-05</v>
+        <v>0.001150539726950228</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.691098027047701e-05</v>
+        <v>6.291724275797606e-06</v>
       </c>
       <c r="CR15" t="n">
-        <v>2.254164610349108e-05</v>
+        <v>0.0003336096997372806</v>
       </c>
       <c r="CS15" t="n">
-        <v>4.114824696443975e-05</v>
+        <v>0.0004331093514338136</v>
       </c>
       <c r="CT15" t="n">
-        <v>5.241196777205914e-05</v>
+        <v>5.892604531254619e-05</v>
       </c>
       <c r="CU15" t="n">
-        <v>4.243348939780844e-06</v>
+        <v>0.0003471453674137592</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.797470870063989e-06</v>
+        <v>8.695723954588175e-05</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.730151391006075e-05</v>
+        <v>0.0007766074850223958</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.183105359814363e-05</v>
+        <v>0.0002293771831318736</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.92723709915299e-05</v>
+        <v>0.0005671029211953282</v>
       </c>
       <c r="CZ15" t="n">
-        <v>8.115403943520505e-06</v>
+        <v>0.0001746686612023041</v>
       </c>
       <c r="DA15" t="n">
-        <v>5.81101903662784e-06</v>
+        <v>0.0002020233951043338</v>
       </c>
       <c r="DB15" t="n">
-        <v>7.848004315746948e-06</v>
+        <v>4.988341243006289e-05</v>
       </c>
       <c r="DC15" t="n">
-        <v>7.091345651133452e-06</v>
+        <v>0.0004314376856200397</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.090361365641002e-06</v>
+        <v>4.397512384457514e-05</v>
       </c>
       <c r="DE15" t="n">
-        <v>2.064691761916038e-05</v>
+        <v>0.0002838827494997531</v>
       </c>
       <c r="DF15" t="n">
-        <v>7.367717444139998e-06</v>
+        <v>0.0007195884827524424</v>
       </c>
       <c r="DG15" t="n">
-        <v>1.396913830831181e-05</v>
+        <v>7.83640134613961e-05</v>
       </c>
       <c r="DH15" t="n">
-        <v>3.615699097281322e-05</v>
+        <v>0.0005995233077555895</v>
       </c>
       <c r="DI15" t="n">
-        <v>8.164449354808312e-06</v>
+        <v>0.001236606505699456</v>
       </c>
       <c r="DJ15" t="n">
-        <v>4.545297997538e-06</v>
+        <v>0.001276231138035655</v>
       </c>
       <c r="DK15" t="n">
-        <v>7.166314389905892e-06</v>
+        <v>0.0001134219564846717</v>
       </c>
       <c r="DL15" t="n">
-        <v>9.59051976678893e-06</v>
+        <v>0.0007443827344104648</v>
       </c>
       <c r="DM15" t="n">
-        <v>3.626733359851642e-06</v>
+        <v>0.0005700958427041769</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.82009398486116e-06</v>
+        <v>0.0001551611348986626</v>
       </c>
       <c r="DO15" t="n">
-        <v>6.567609943886055e-06</v>
+        <v>0.0005413424805738032</v>
       </c>
       <c r="DP15" t="n">
-        <v>1.471194445912261e-05</v>
+        <v>0.0002910670009441674</v>
       </c>
       <c r="DQ15" t="n">
-        <v>1.561728095111903e-05</v>
+        <v>0.0006826499011367559</v>
       </c>
       <c r="DR15" t="n">
-        <v>1.998847983486485e-05</v>
+        <v>5.88797265663743e-05</v>
       </c>
       <c r="DS15" t="n">
-        <v>1.217449494106404e-06</v>
+        <v>1.784197775123175e-05</v>
       </c>
       <c r="DT15" t="n">
-        <v>3.403913069632836e-06</v>
+        <v>0.000341033301083371</v>
       </c>
       <c r="DU15" t="n">
-        <v>1.141366647061659e-05</v>
+        <v>0.000269468902843073</v>
       </c>
       <c r="DV15" t="n">
-        <v>1.446531223336933e-05</v>
+        <v>0.0003092691476922482</v>
       </c>
       <c r="DW15" t="n">
-        <v>1.363139563181903e-05</v>
+        <v>0.0006313779740594327</v>
       </c>
       <c r="DX15" t="n">
-        <v>2.30668083531782e-05</v>
+        <v>4.599196836352348e-05</v>
       </c>
       <c r="DY15" t="n">
-        <v>1.745267582009546e-05</v>
+        <v>0.0004983848193660378</v>
       </c>
       <c r="DZ15" t="n">
-        <v>1.382024765916867e-05</v>
+        <v>0.0002730858395807445</v>
       </c>
       <c r="EA15" t="n">
-        <v>2.793910198306548e-06</v>
+        <v>0.0006943917833268642</v>
       </c>
       <c r="EB15" t="n">
-        <v>8.643984983791597e-06</v>
+        <v>0.0005742252105847001</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.078583136404632e-05</v>
+        <v>9.800246334634721e-05</v>
       </c>
       <c r="ED15" t="n">
-        <v>8.453667760477401e-06</v>
+        <v>0.001790985930711031</v>
       </c>
       <c r="EE15" t="n">
-        <v>3.028644641744904e-06</v>
+        <v>0.001099857967346907</v>
       </c>
       <c r="EF15" t="n">
-        <v>7.46721798350336e-06</v>
+        <v>1.198938116431236e-05</v>
       </c>
       <c r="EG15" t="n">
-        <v>1.981232708203606e-05</v>
+        <v>8.411800808971748e-05</v>
       </c>
       <c r="EH15" t="n">
-        <v>1.177339527203003e-05</v>
+        <v>2.890397445298731e-05</v>
       </c>
       <c r="EI15" t="n">
-        <v>1.420025728293695e-05</v>
+        <v>0.001241959049366415</v>
       </c>
       <c r="EJ15" t="n">
-        <v>2.876070902857464e-05</v>
+        <v>0.0002325713139725849</v>
       </c>
       <c r="EK15" t="n">
-        <v>4.983002327207942e-06</v>
+        <v>0.0001193904608953744</v>
       </c>
       <c r="EL15" t="n">
-        <v>3.572313289623708e-06</v>
+        <v>6.480468437075615e-05</v>
       </c>
       <c r="EM15" t="n">
-        <v>2.393059503447148e-06</v>
+        <v>2.357368794037029e-05</v>
       </c>
       <c r="EN15" t="n">
-        <v>9.835198397922795e-06</v>
+        <v>7.879541954025626e-05</v>
       </c>
       <c r="EO15" t="n">
-        <v>2.396552190475632e-06</v>
+        <v>0.0003038525173906237</v>
       </c>
       <c r="EP15" t="n">
-        <v>3.043637843802571e-05</v>
+        <v>0.0004594677011482418</v>
       </c>
       <c r="EQ15" t="n">
-        <v>1.330436134594493e-05</v>
+        <v>0.0006275436608120799</v>
       </c>
       <c r="ER15" t="n">
-        <v>1.010694722936023e-05</v>
+        <v>0.0001061464136000723</v>
       </c>
       <c r="ES15" t="n">
-        <v>3.087116056121886e-06</v>
+        <v>0.0007035208400338888</v>
       </c>
       <c r="ET15" t="n">
-        <v>6.374509212037083e-06</v>
+        <v>0.000397009338485077</v>
       </c>
       <c r="EU15" t="n">
-        <v>2.27688615268562e-05</v>
+        <v>0.0001141921602538787</v>
       </c>
       <c r="EV15" t="n">
-        <v>2.107042564603034e-05</v>
+        <v>0.0001982631365535781</v>
       </c>
       <c r="EW15" t="n">
-        <v>1.86971592484042e-05</v>
+        <v>0.000109881249954924</v>
       </c>
       <c r="EX15" t="n">
-        <v>4.628474471246591e-06</v>
+        <v>5.31854821019806e-05</v>
       </c>
       <c r="EY15" t="n">
-        <v>2.826224954333156e-05</v>
+        <v>0.001020255964249372</v>
       </c>
       <c r="EZ15" t="n">
-        <v>7.44057842894108e-06</v>
+        <v>0.0001096460910048336</v>
       </c>
       <c r="FA15" t="n">
-        <v>1.28882611534209e-05</v>
+        <v>0.0005347461556084454</v>
       </c>
       <c r="FB15" t="n">
-        <v>3.754734052563435e-06</v>
+        <v>0.0002016859216382727</v>
       </c>
       <c r="FC15" t="n">
-        <v>3.562623533071019e-06</v>
+        <v>6.605186354136094e-05</v>
       </c>
       <c r="FD15" t="n">
-        <v>7.49964374335832e-06</v>
+        <v>0.0001467923575546592</v>
       </c>
       <c r="FE15" t="n">
-        <v>2.107265117956558e-06</v>
+        <v>0.0004504529933910817</v>
       </c>
       <c r="FF15" t="n">
-        <v>5.070689894637326e-06</v>
+        <v>3.212667797924951e-05</v>
       </c>
       <c r="FG15" t="n">
-        <v>5.608221727015916e-07</v>
+        <v>0.0001748993672663346</v>
       </c>
       <c r="FH15" t="n">
-        <v>1.462071941205068e-05</v>
+        <v>0.000895039935130626</v>
       </c>
       <c r="FI15" t="n">
-        <v>3.16032710543368e-05</v>
+        <v>0.0005301694036461413</v>
       </c>
       <c r="FJ15" t="n">
-        <v>1.523567334515974e-05</v>
+        <v>0.0008512679487466812</v>
       </c>
       <c r="FK15" t="n">
-        <v>1.345145210507326e-05</v>
+        <v>0.0001176848891191185</v>
       </c>
       <c r="FL15" t="n">
-        <v>9.932226930686738e-06</v>
+        <v>0.0009086006321012974</v>
       </c>
       <c r="FM15" t="n">
-        <v>5.091942057333654e-06</v>
+        <v>0.0001312139356741682</v>
       </c>
       <c r="FN15" t="n">
-        <v>8.290892310469644e-07</v>
+        <v>4.542423994280398e-05</v>
       </c>
       <c r="FO15" t="n">
-        <v>7.719829227426089e-06</v>
+        <v>0.001447672606445849</v>
       </c>
       <c r="FP15" t="n">
-        <v>2.22277103603119e-05</v>
+        <v>0.0001666359894443303</v>
       </c>
       <c r="FQ15" t="n">
-        <v>3.627976866482641e-06</v>
+        <v>9.752730693435296e-05</v>
       </c>
       <c r="FR15" t="n">
-        <v>3.699088847497478e-05</v>
+        <v>0.000699116731993854</v>
       </c>
       <c r="FS15" t="n">
-        <v>2.131367909896653e-05</v>
+        <v>0.0002986631589010358</v>
       </c>
       <c r="FT15" t="n">
-        <v>1.562626130180433e-05</v>
+        <v>0.00134357693605125</v>
       </c>
       <c r="FU15" t="n">
-        <v>1.988502481253818e-05</v>
+        <v>0.001088585588149726</v>
       </c>
       <c r="FV15" t="n">
-        <v>1.323123797192238e-06</v>
+        <v>0.0008001773385331035</v>
       </c>
       <c r="FW15" t="n">
-        <v>5.949422302364837e-06</v>
+        <v>0.001191486022435129</v>
       </c>
       <c r="FX15" t="n">
-        <v>9.704136573418509e-06</v>
+        <v>8.127428009174764e-05</v>
       </c>
       <c r="FY15" t="n">
-        <v>2.280475564475637e-05</v>
+        <v>0.0002157049893867224</v>
       </c>
       <c r="FZ15" t="n">
-        <v>1.180868457595352e-05</v>
+        <v>0.0002300797787029296</v>
       </c>
       <c r="GA15" t="n">
-        <v>1.409775086358422e-05</v>
+        <v>0.0006399904377758503</v>
       </c>
       <c r="GB15" t="n">
-        <v>8.224252269428689e-06</v>
+        <v>0.0002738132316153497</v>
       </c>
       <c r="GC15" t="n">
-        <v>8.337044164363761e-06</v>
+        <v>0.001407119096256793</v>
       </c>
       <c r="GD15" t="n">
-        <v>2.767593468888663e-05</v>
+        <v>0.0009123806958086789</v>
       </c>
       <c r="GE15" t="n">
-        <v>6.250327714951709e-05</v>
+        <v>0.000526569492649287</v>
       </c>
       <c r="GF15" t="n">
-        <v>7.637973794771824e-06</v>
+        <v>0.0004202833806630224</v>
       </c>
       <c r="GG15" t="n">
-        <v>1.395175604557153e-05</v>
+        <v>0.0002665840729605407</v>
       </c>
     </row>
   </sheetData>
